--- a/outputs/sesi_pdf_relatorio_qualidade.xlsx
+++ b/outputs/sesi_pdf_relatorio_qualidade.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M219"/>
+  <dimension ref="A1:M215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,18 +523,18 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Índice — CONTRATOS, CONVÊNIOS E OUTRAS FORMAS DE AJUSTE</t>
+          <t>Índice — DEMONSTRAÇÃO DE RESULTADOS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Contratos 2022 (PDF) 234,7 KB</t>
+          <t>Abrir Mapa Estratégico em PDF 5 mb</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Transparência (índice) | CONTRATOS, CONVÊNIOS E OUTRAS FORMAS DE AJUSTE</t>
+          <t>Transparência (índice) | DEMONSTRAÇÃO DE RESULTADOS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20230209_transparencia_plano_de_contingencia_contratos_sesi_2022_pdf.pdf</t>
+          <t>sesi_mapa_estrategico_sistemico_2025-2027_1.pdf</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/a7/00/a700e132-d651-42f3-aeb8-6fc2fe1f5bb7/20230209_transparencia_plano_de_contingencia_contratos_sesi_2022_pdf.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/86/46/864686df-c7ee-4b7f-90dc-4e930ebaa26d/sesi_mapa_estrategico_sistemico_2025-2027_1.pdf</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -563,7 +563,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -578,18 +578,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Índice — CONTRATOS, CONVÊNIOS E OUTRAS FORMAS DE AJUSTE</t>
+          <t>Índice — DEMONSTRAÇÃO DE RESULTADOS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Contratos 2021 (PDF) 169,8 KB</t>
+          <t>Abrir Mapa Estratégico em PDF 5 mb</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Transparência (índice) | CONTRATOS, CONVÊNIOS E OUTRAS FORMAS DE AJUSTE</t>
+          <t>Transparência (índice) | DEMONSTRAÇÃO DE RESULTADOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20220126_plano_de_contingencia_contratos_sesi_dn.pdf</t>
+          <t>placeholder-pdf.pdf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/0e/b9/0eb91945-0ddb-444c-9e56-be0837749c73/20220126_plano_de_contingencia_contratos_sesi_dn.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/4a/96/4a96970b-c5d5-4995-b404-21396c74564b/placeholder-pdf.pdf</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -618,7 +618,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -633,18 +633,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Índice — CONTRATOS, CONVÊNIOS E OUTRAS FORMAS DE AJUSTE</t>
+          <t>Índice — DEMONSTRAÇÃO DE RESULTADOS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Convênios 2022 (PDF) 82,5 KB</t>
+          <t>Relatório de Gestão 2025 36 Mb</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Transparência (índice) | CONTRATOS, CONVÊNIOS E OUTRAS FORMAS DE AJUSTE</t>
+          <t>Transparência (índice) | DEMONSTRAÇÃO DE RESULTADOS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>convenios_-_sesi_2022.pdf</t>
+          <t>relatorio_sesi_2025_web.pdf</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/51/26/51269a46-7be7-4168-85d4-f212af9e588d/convenios_-_sesi_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/a2/fe/a2fe2530-c560-4651-b4f6-a75545065518/relatorio_sesi_2025_web.pdf</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -670,10 +670,12 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>35156.53</v>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -688,18 +690,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Índice — CONTRATOS, CONVÊNIOS E OUTRAS FORMAS DE AJUSTE</t>
+          <t>Índice — DEMONSTRAÇÃO DE RESULTADOS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Convênios 2021 (PDF) 35,5 KB</t>
+          <t>Relatório de Gestão 2024 11,7 Mb</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Transparência (índice) | CONTRATOS, CONVÊNIOS E OUTRAS FORMAS DE AJUSTE</t>
+          <t>Transparência (índice) | DEMONSTRAÇÃO DE RESULTADOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -709,12 +711,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>convenios_-_sesi_2021.pdf</t>
+          <t>sesi_relatorio_gestao_2024_web.pdf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/c0/e2/c0e2be32-0431-45b5-9ced-f84f19b83ab2/convenios_-_sesi_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/14/dd/14dd2c28-9a72-4ace-ba92-c16680e92bd9/sesi_relatorio_gestao_2024_web.pdf</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -725,10 +727,12 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>11422.32</v>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -748,7 +752,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Abrir Mapa Estratégico em PDF 5 mb</t>
+          <t>Relatório de Gestão 2023 5,8 Mb</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -764,12 +768,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>sesi_mapa_estrategico_sistemico_2025-2027_1.pdf</t>
+          <t>sesi_relatorio_gestao_2023.pdf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/86/46/864686df-c7ee-4b7f-90dc-4e930ebaa26d/sesi_mapa_estrategico_sistemico_2025-2027_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/53/03/5303f305-b21b-489f-ade3-01acea2c548f/sesi_relatorio_gestao_2023.pdf</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -783,7 +787,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -803,7 +807,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abrir Mapa Estratégico em PDF 5 mb</t>
+          <t>Relatório de Gestão 2022 17,2 Mb</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -819,12 +823,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>placeholder-pdf.pdf</t>
+          <t>relatorio_de_gestao_sesi_2022_20230330.pdf</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/4a/96/4a96970b-c5d5-4995-b404-21396c74564b/placeholder-pdf.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/bb/be/bbbee611-4ee1-45e2-a246-6443eda8e15c/relatorio_de_gestao_sesi_2022_20230330.pdf</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -835,10 +839,12 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>17156.41</v>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -858,7 +864,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Relatório de Gestão 2025 36 Mb</t>
+          <t>Relatório de Gestão 2021 7,2 Mb</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -874,12 +880,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>relatorio_sesi_2025_web.pdf</t>
+          <t>sesi_relatorio_de_gestao_2021_completo_202203024_16h.pdf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/a2/fe/a2fe2530-c560-4651-b4f6-a75545065518/relatorio_sesi_2025_web.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/47/c2/47c21a11-9320-4725-8fe7-0e4d96d12d62/sesi_relatorio_de_gestao_2021_completo_202203024_16h.pdf</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -890,12 +896,10 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>35156.53</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -915,7 +919,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Relatório de Gestão 2024 11,7 Mb</t>
+          <t>Relatório de Gestão 2020 5,8 Mb</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -931,12 +935,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>sesi_relatorio_gestao_2024_web.pdf</t>
+          <t>sesi_relatorio_de_gestao_20210330_final_conselho_vf.pdf</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/14/dd/14dd2c28-9a72-4ace-ba92-c16680e92bd9/sesi_relatorio_gestao_2024_web.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/fd/0e/fd0e6fc9-1342-4791-a5e3-b160b8f0da0d/sesi_relatorio_de_gestao_20210330_final_conselho_vf.pdf</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -947,12 +951,10 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>11422.32</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -967,18 +969,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Índice — DEMONSTRAÇÃO DE RESULTADOS</t>
+          <t>Índice — DEMONSTRAÇÕES CONTÁBEIS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Relatório de Gestão 2023 5,8 Mb</t>
+          <t>Relatório de Auditoria Independente sobre as Demonstrações Contábeis - 179,9 KB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Transparência (índice) | DEMONSTRAÇÃO DE RESULTADOS</t>
+          <t>Transparência (índice) | DEMONSTRAÇÕES CONTÁBEIS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -988,12 +990,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>sesi_relatorio_gestao_2023.pdf</t>
+          <t>1-sesi-relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis_2025.pdf</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/53/03/5303f305-b21b-489f-ade3-01acea2c548f/sesi_relatorio_gestao_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/96/ac/96ac0ba7-52ca-4ac8-b80b-b63dc64265be/1-sesi-relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis_2025.pdf</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1007,7 +1009,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1022,18 +1024,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Índice — DEMONSTRAÇÃO DE RESULTADOS</t>
+          <t>Índice — DEMONSTRAÇÕES CONTÁBEIS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Relatório de Gestão 2022 17,2 Mb</t>
+          <t>Balanço Patrimonial - PDF - 750,9 KB</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Transparência (índice) | DEMONSTRAÇÃO DE RESULTADOS</t>
+          <t>Transparência (índice) | DEMONSTRAÇÕES CONTÁBEIS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1043,12 +1045,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>relatorio_de_gestao_sesi_2022_20230330.pdf</t>
+          <t>2-sesi_balanco_patrimonial_2025.pdf</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/bb/be/bbbee611-4ee1-45e2-a246-6443eda8e15c/relatorio_de_gestao_sesi_2022_20230330.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/b9/f1/b9f19d2f-996e-4c7d-9404-ddb70ce5027c/2-sesi_balanco_patrimonial_2025.pdf</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1059,12 +1061,10 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>17156.41</v>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1079,18 +1079,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Índice — DEMONSTRAÇÃO DE RESULTADOS</t>
+          <t>Índice — DEMONSTRAÇÕES CONTÁBEIS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Relatório de Gestão 2021 7,2 Mb</t>
+          <t>Balanço Orçamentário - PDF - 690,3 KB</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Transparência (índice) | DEMONSTRAÇÃO DE RESULTADOS</t>
+          <t>Transparência (índice) | DEMONSTRAÇÕES CONTÁBEIS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>sesi_relatorio_de_gestao_2021_completo_202203024_16h.pdf</t>
+          <t>3-sesi_balanco_orcamentario_2025.pdf</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/47/c2/47c21a11-9320-4725-8fe7-0e4d96d12d62/sesi_relatorio_de_gestao_2021_completo_202203024_16h.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/c4/e3/c4e3d337-5020-41a6-a98a-9d31032ace12/3-sesi_balanco_orcamentario_2025.pdf</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1119,7 +1119,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1134,18 +1134,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Índice — DEMONSTRAÇÃO DE RESULTADOS</t>
+          <t>Índice — DEMONSTRAÇÕES CONTÁBEIS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Relatório de Gestão 2020 5,8 Mb</t>
+          <t>Balanço Financeiro - PDF - 708,3 KB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Transparência (índice) | DEMONSTRAÇÃO DE RESULTADOS</t>
+          <t>Transparência (índice) | DEMONSTRAÇÕES CONTÁBEIS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>sesi_relatorio_de_gestao_20210330_final_conselho_vf.pdf</t>
+          <t>4-sesi_balanco_financeiro_2025.pdf</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/fd/0e/fd0e6fc9-1342-4791-a5e3-b160b8f0da0d/sesi_relatorio_de_gestao_20210330_final_conselho_vf.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/da/3f/da3fd9c9-4833-4c87-978e-d92acf4fc0de/4-sesi_balanco_financeiro_2025.pdf</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1174,7 +1174,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Relatório de Auditoria Independente sobre as Demonstrações Contábeis - 179,9 KB</t>
+          <t>Demonstração das Variações Patrimoniais - PDF - 838,7 KB</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1-sesi-relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis_2025.pdf</t>
+          <t>5-sesi_demonstracao_das_variacoes_patrimoniais_2025.pdf</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/96/ac/96ac0ba7-52ca-4ac8-b80b-b63dc64265be/1-sesi-relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/27/6b/276bcf2f-7cd1-4dba-ac74-d047099dbf81/5-sesi_demonstracao_das_variacoes_patrimoniais_2025.pdf</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1229,7 +1229,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Balanço Patrimonial - PDF - 750,9 KB</t>
+          <t>Demonstração de Fluxo de Caixa - PDF - 542,1 KB</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2-sesi_balanco_patrimonial_2025.pdf</t>
+          <t>6-sesi_demonstracao_de__fluxo_de_caixa_2025.pdf</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/b9/f1/b9f19d2f-996e-4c7d-9404-ddb70ce5027c/2-sesi_balanco_patrimonial_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f6/3c/f63cca95-131d-4d45-b12d-39428325438c/6-sesi_demonstracao_de__fluxo_de_caixa_2025.pdf</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1284,7 +1284,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Balanço Orçamentário - PDF - 690,3 KB</t>
+          <t>Demonstração das Mutações do Patrimônio Líquido - PDF - 320,7 KB</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3-sesi_balanco_orcamentario_2025.pdf</t>
+          <t>7-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2025.pdf</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/c4/e3/c4e3d337-5020-41a6-a98a-9d31032ace12/3-sesi_balanco_orcamentario_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/cb/4a/cb4a6c2d-4684-4fd3-bac9-87fb224d88db/7-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2025.pdf</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1339,7 +1339,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Balanço Financeiro - PDF - 708,3 KB</t>
+          <t>Demonstração de Resultado Abrangente - PDF - 317,8 KB</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4-sesi_balanco_financeiro_2025.pdf</t>
+          <t>8-sesi_demonstracao_de_resultado_abrangente_2025.pdf</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/da/3f/da3fd9c9-4833-4c87-978e-d92acf4fc0de/4-sesi_balanco_financeiro_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/cc/cb/cccbc12f-0318-487b-9930-ce1cb11a53d6/8-sesi_demonstracao_de_resultado_abrangente_2025.pdf</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1394,7 +1394,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Demonstração das Variações Patrimoniais - PDF - 838,7 KB</t>
+          <t>Notas Explicativas. - 1,5 MB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5-sesi_demonstracao_das_variacoes_patrimoniais_2025.pdf</t>
+          <t>9-sesi_-_notas_explicativas_2025.pdf</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/27/6b/276bcf2f-7cd1-4dba-ac74-d047099dbf81/5-sesi_demonstracao_das_variacoes_patrimoniais_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/a5/8a/a58a1a66-f38a-4d7b-8d87-ccadbc660176/9-sesi_-_notas_explicativas_2025.pdf</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1449,7 +1449,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Demonstração de Fluxo de Caixa - PDF - 542,1 KB</t>
+          <t>Relatório de Auditoria Independente sobre as Demonstrações Contábeis - 299,5 KB</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6-sesi_demonstracao_de__fluxo_de_caixa_2025.pdf</t>
+          <t>1-relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis.pdf</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f6/3c/f63cca95-131d-4d45-b12d-39428325438c/6-sesi_demonstracao_de__fluxo_de_caixa_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/88/0f/880f4d26-dda5-4ccd-87bb-d39e13ba4a0e/1-relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis.pdf</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1504,7 +1504,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Demonstração das Mutações do Patrimônio Líquido - PDF - 320,7 KB</t>
+          <t>Balanço Patrimonial - PDF - 125,0 KB</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2025.pdf</t>
+          <t>2-sesi_balanco_patrimonial_2024.pdf</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/cb/4a/cb4a6c2d-4684-4fd3-bac9-87fb224d88db/7-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/e1/6e/e16efab7-19b2-4ccc-b422-da8428a1123a/2-sesi_balanco_patrimonial_2024.pdf</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1559,7 +1559,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Demonstração de Resultado Abrangente - PDF - 317,8 KB</t>
+          <t>Balanço Orçamentário - PDF - 756,4 KB</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8-sesi_demonstracao_de_resultado_abrangente_2025.pdf</t>
+          <t>3-sesi_balanco_orcamentario_2024.pdf</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/cc/cb/cccbc12f-0318-487b-9930-ce1cb11a53d6/8-sesi_demonstracao_de_resultado_abrangente_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f0/bd/f0bdcede-5399-4239-88af-3b179ddf1c71/3-sesi_balanco_orcamentario_2024.pdf</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1614,7 +1614,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Notas Explicativas. - 1,5 MB</t>
+          <t>Balanço Financeiro - PDF - 740,5 KB</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>9-sesi_-_notas_explicativas_2025.pdf</t>
+          <t>4-sesi_balanco_financeiro_2024.pdf</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/a5/8a/a58a1a66-f38a-4d7b-8d87-ccadbc660176/9-sesi_-_notas_explicativas_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/22/dd/22dd5e94-3bc5-42cf-81e3-754947cbab5e/4-sesi_balanco_financeiro_2024.pdf</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1669,7 +1669,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Relatório de Auditoria Independente sobre as Demonstrações Contábeis - 299,5 KB</t>
+          <t>Demonstração das Variações Patrimoniais - PDF - 748,0 KB</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1-relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis.pdf</t>
+          <t>5-sesi_demonstracao_das_variacoes_patrimoniais_2024.pdf</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/88/0f/880f4d26-dda5-4ccd-87bb-d39e13ba4a0e/1-relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/1e/15/1e15f9ff-01c8-45f0-ac8b-43d91a921d79/5-sesi_demonstracao_das_variacoes_patrimoniais_2024.pdf</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1724,7 +1724,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Balanço Patrimonial - PDF - 125,0 KB</t>
+          <t>Demonstração de Fluxo de Caixa - PDF - 461,9 KB</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2-sesi_balanco_patrimonial_2024.pdf</t>
+          <t>6-sesi_demonstracao_de__fluxo_de_caixa_2024.pdf</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/e1/6e/e16efab7-19b2-4ccc-b422-da8428a1123a/2-sesi_balanco_patrimonial_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/27/7e/277e93db-6d20-43f7-b9a0-ae3fbd28ff80/6-sesi_demonstracao_de__fluxo_de_caixa_2024.pdf</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1779,7 +1779,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Balanço Orçamentário - PDF - 756,4 KB</t>
+          <t>Demonstração das Mutações do Patrimônio Líquido - PDF - 279,4 KB</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3-sesi_balanco_orcamentario_2024.pdf</t>
+          <t>7-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2024.pdf</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f0/bd/f0bdcede-5399-4239-88af-3b179ddf1c71/3-sesi_balanco_orcamentario_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/5a/4d/5a4d913e-f675-44d6-9433-36ef78ce5ecf/7-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2024.pdf</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1834,7 +1834,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Balanço Financeiro - PDF - 740,5 KB</t>
+          <t>Demonstração de Resultado Abrangente - PDF - 280,6 KB</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4-sesi_balanco_financeiro_2024.pdf</t>
+          <t>8-sesi_demonstracao_de_resultado_abrangente_2024.pdf</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/22/dd/22dd5e94-3bc5-42cf-81e3-754947cbab5e/4-sesi_balanco_financeiro_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/14/76/147658c3-eb49-4452-b1a3-a1318276f559/8-sesi_demonstracao_de_resultado_abrangente_2024.pdf</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1889,7 +1889,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Demonstração das Variações Patrimoniais - PDF - 748,0 KB</t>
+          <t>Notas Explicativas. - 1,3 MB</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5-sesi_demonstracao_das_variacoes_patrimoniais_2024.pdf</t>
+          <t>9-sesi_-_notas_explicativas_2024.pdf</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/1e/15/1e15f9ff-01c8-45f0-ac8b-43d91a921d79/5-sesi_demonstracao_das_variacoes_patrimoniais_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/96/42/9642d4a7-559b-4153-ba70-8b0ba694cda7/9-sesi_-_notas_explicativas_2024.pdf</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1944,7 +1944,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Demonstração de Fluxo de Caixa - PDF - 461,9 KB</t>
+          <t>Relatório de Auditoria Independente sobre as Demonstrações Contábeis - 212,7 KB</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6-sesi_demonstracao_de__fluxo_de_caixa_2024.pdf</t>
+          <t>1-sesi_relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis.pdf</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/27/7e/277e93db-6d20-43f7-b9a0-ae3fbd28ff80/6-sesi_demonstracao_de__fluxo_de_caixa_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/a8/12/a812417e-d6e0-45da-95b5-601d41d3de25/1-sesi_relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis.pdf</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1999,7 +1999,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Demonstração das Mutações do Patrimônio Líquido - PDF - 279,4 KB</t>
+          <t>Balanço Patrimonial - PDF - 172,8 KB</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2024.pdf</t>
+          <t>2-sesi_balanco_patrimonial_2023.pdf</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/5a/4d/5a4d913e-f675-44d6-9433-36ef78ce5ecf/7-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/05/da/05da4aa7-8307-419d-bc2a-e586fc3ed729/2-sesi_balanco_patrimonial_2023.pdf</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2054,7 +2054,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Demonstração de Resultado Abrangente - PDF - 280,6 KB</t>
+          <t>Balanço Orçamentário - PDF - 174,0 KB</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8-sesi_demonstracao_de_resultado_abrangente_2024.pdf</t>
+          <t>3-sesi_balanco_orcamentario_2023.pdf</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/14/76/147658c3-eb49-4452-b1a3-a1318276f559/8-sesi_demonstracao_de_resultado_abrangente_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/ba/ba/baba3e92-2963-4156-abbe-50bf569a6cd0/3-sesi_balanco_orcamentario_2023.pdf</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2109,7 +2109,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Notas Explicativas. - 1,3 MB</t>
+          <t>Balanço Financeiro - PDF - 175,5 KB</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9-sesi_-_notas_explicativas_2024.pdf</t>
+          <t>4-sesi_balanco_financeiro_2023.pdf</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/96/42/9642d4a7-559b-4153-ba70-8b0ba694cda7/9-sesi_-_notas_explicativas_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/47/fb/47fbb00f-90db-4431-9ae3-8d15b882594c/4-sesi_balanco_financeiro_2023.pdf</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2164,7 +2164,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Relatório de Auditoria Independente sobre as Demonstrações Contábeis - 212,7 KB</t>
+          <t>Demonstração das Variações Patrimoniais - PDF - 173,3 KB</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1-sesi_relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis.pdf</t>
+          <t>5-sesi_demonstracao_das_variacoes_patrimoniais_2023.pdf</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/a8/12/a812417e-d6e0-45da-95b5-601d41d3de25/1-sesi_relatorio_do_auditor_independente_sobre_as_demonstracoes_contabeis.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/2f/a2/2fa257d1-a02e-4bcf-8130-55698ebb5f59/5-sesi_demonstracao_das_variacoes_patrimoniais_2023.pdf</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2219,7 +2219,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Balanço Patrimonial - PDF - 172,8 KB</t>
+          <t>Demonstração de Fluxo de Caixa - PDF - 166,2 KB</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2255,12 +2255,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2-sesi_balanco_patrimonial_2023.pdf</t>
+          <t>7-sesi_demonstracao_de_fluxo_de_caixa_2023.pdf</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/05/da/05da4aa7-8307-419d-bc2a-e586fc3ed729/2-sesi_balanco_patrimonial_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/fc/9d/fc9d2bf4-780b-40b1-b816-26ed54207ea6/7-sesi_demonstracao_de_fluxo_de_caixa_2023.pdf</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2274,7 +2274,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Balanço Orçamentário - PDF - 174,0 KB</t>
+          <t>Demonstração das Mutações do Patrimônio Líquido - PDF - 164,7 KB</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2310,12 +2310,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3-sesi_balanco_orcamentario_2023.pdf</t>
+          <t>6-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2023.pdf</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/ba/ba/baba3e92-2963-4156-abbe-50bf569a6cd0/3-sesi_balanco_orcamentario_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f4/07/f4070b60-cc31-43d0-b411-179b2cfe99ad/6-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2023.pdf</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2329,7 +2329,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Balanço Financeiro - PDF - 175,5 KB</t>
+          <t>Demonstração de Resultado Abrangente - PDF - 163,4 KB</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2365,12 +2365,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4-sesi_balanco_financeiro_2023.pdf</t>
+          <t>8-sesi_demonstracao_de_resultado_abrangente_2023.pdf</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/47/fb/47fbb00f-90db-4431-9ae3-8d15b882594c/4-sesi_balanco_financeiro_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/d4/aa/d4aa0543-74ae-4658-a329-264487569e31/8-sesi_demonstracao_de_resultado_abrangente_2023.pdf</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2384,7 +2384,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Demonstração das Variações Patrimoniais - PDF - 173,3 KB</t>
+          <t>Notas Explicativas. - 1,4 MB</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5-sesi_demonstracao_das_variacoes_patrimoniais_2023.pdf</t>
+          <t>9-sesi_notas_explicativas_2023.pdf</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/2f/a2/2fa257d1-a02e-4bcf-8130-55698ebb5f59/5-sesi_demonstracao_das_variacoes_patrimoniais_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/02/3a/023afc07-c5d3-47f9-a10f-17b39292d4b5/9-sesi_notas_explicativas_2023.pdf</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2439,7 +2439,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Demonstração de Fluxo de Caixa - PDF - 166,2 KB</t>
+          <t>Balanço Patrimonial - PDF - 178,3 KB</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7-sesi_demonstracao_de_fluxo_de_caixa_2023.pdf</t>
+          <t>1_-_sesi_balanco_patrimonial_2022.pdf</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/fc/9d/fc9d2bf4-780b-40b1-b816-26ed54207ea6/7-sesi_demonstracao_de_fluxo_de_caixa_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/b1/d2/b1d2a928-6a4d-4041-960b-feed1256481d/1_-_sesi_balanco_patrimonial_2022.pdf</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2494,7 +2494,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Demonstração das Mutações do Patrimônio Líquido - PDF - 164,7 KB</t>
+          <t>Balanço Orçamentário - PDF - 179,3 KB</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2023.pdf</t>
+          <t>2_-_sesi_balanco_orcamentario_2022.pdf</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f4/07/f4070b60-cc31-43d0-b411-179b2cfe99ad/6-sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/6b/9e/6b9e518c-1458-4406-8354-07b95b653caf/2_-_sesi_balanco_orcamentario_2022.pdf</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2549,7 +2549,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Demonstração de Resultado Abrangente - PDF - 163,4 KB</t>
+          <t>Balanço Financeiro - PDF - 181,6 KB</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2585,12 +2585,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8-sesi_demonstracao_de_resultado_abrangente_2023.pdf</t>
+          <t>3_-_sesi_balanco_financeiro_2022.pdf</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/d4/aa/d4aa0543-74ae-4658-a329-264487569e31/8-sesi_demonstracao_de_resultado_abrangente_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/c0/42/c042e91e-b726-4c6e-aa64-14ea6d8b59c0/3_-_sesi_balanco_financeiro_2022.pdf</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2604,7 +2604,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Notas Explicativas. - 1,4 MB</t>
+          <t>Demonstração das Variações Patrimoniais - PDF - 182,5 KB</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>9-sesi_notas_explicativas_2023.pdf</t>
+          <t>4_-_sesi_demonstracao_das_variacoes_patrimoniais_2022.pdf</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/02/3a/023afc07-c5d3-47f9-a10f-17b39292d4b5/9-sesi_notas_explicativas_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/59/a7/59a7e78c-2615-43bb-9bbf-43fcbe535642/4_-_sesi_demonstracao_das_variacoes_patrimoniais_2022.pdf</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2659,7 +2659,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Balanço Patrimonial - PDF - 178,3 KB</t>
+          <t>Demonstração de Fluxo de Caixa - PDF - 172,4 KB</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1_-_sesi_balanco_patrimonial_2022.pdf</t>
+          <t>5_-_sesi_demonstracao_de_fluxo_de_caixa_2022.pdf</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/b1/d2/b1d2a928-6a4d-4041-960b-feed1256481d/1_-_sesi_balanco_patrimonial_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f5/c2/f5c27725-d7b2-4647-b572-c604312f7b21/5_-_sesi_demonstracao_de_fluxo_de_caixa_2022.pdf</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2714,7 +2714,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Balanço Orçamentário - PDF - 179,3 KB</t>
+          <t>Demonstração das Mutações do Patrimônio Líquido - PDF - 170,9 KB</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2_-_sesi_balanco_orcamentario_2022.pdf</t>
+          <t>6_-_sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2022.pdf</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/6b/9e/6b9e518c-1458-4406-8354-07b95b653caf/2_-_sesi_balanco_orcamentario_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/18/9d/189d30dd-fdb8-4aff-9acc-e4e9a131a93e/6_-_sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2022.pdf</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2769,7 +2769,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Balanço Financeiro - PDF - 181,6 KB</t>
+          <t>Demonstração de Resultado Abrangente - PDF - 169,6 KB</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3_-_sesi_balanco_financeiro_2022.pdf</t>
+          <t>7_-_sesi_demonstracao_de_resultado_abrangente_2022.pdf</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/c0/42/c042e91e-b726-4c6e-aa64-14ea6d8b59c0/3_-_sesi_balanco_financeiro_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/b6/37/b637b159-aad2-426f-b85b-c52bfb58a3f8/7_-_sesi_demonstracao_de_resultado_abrangente_2022.pdf</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2824,7 +2824,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Demonstração das Variações Patrimoniais - PDF - 182,5 KB</t>
+          <t>Notas Explicativas. - 1,5 MB</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2860,12 +2860,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4_-_sesi_demonstracao_das_variacoes_patrimoniais_2022.pdf</t>
+          <t>8_-_sesi_notas_explicativas_2022.pdf</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/59/a7/59a7e78c-2615-43bb-9bbf-43fcbe535642/4_-_sesi_demonstracao_das_variacoes_patrimoniais_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/03/62/0362087c-775a-45b5-9f5c-605b9bdad868/8_-_sesi_notas_explicativas_2022.pdf</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2879,7 +2879,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Demonstração de Fluxo de Caixa - PDF - 172,4 KB</t>
+          <t>Balanço Patrimonial; - 178,3 KB</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5_-_sesi_demonstracao_de_fluxo_de_caixa_2022.pdf</t>
+          <t>sesi_balanco_patrimonial_2021.pdf</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f5/c2/f5c27725-d7b2-4647-b572-c604312f7b21/5_-_sesi_demonstracao_de_fluxo_de_caixa_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/6c/eb/6ceb4b76-b947-4461-bdf2-c66c0ec1625c/sesi_balanco_patrimonial_2021.pdf</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -2934,7 +2934,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Demonstração das Mutações do Patrimônio Líquido - PDF - 170,9 KB</t>
+          <t>Balanço Orçamentário; - 179,8 KB</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2970,12 +2970,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6_-_sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2022.pdf</t>
+          <t>sesi_balanco_orcamentario_2021.pdf</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/18/9d/189d30dd-fdb8-4aff-9acc-e4e9a131a93e/6_-_sesi_demonstracao_das_mutacoes_do_patrimonio_liquido_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/96/2f/962fcc6f-95f6-47e5-af30-03806b938d82/sesi_balanco_orcamentario_2021.pdf</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2989,7 +2989,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Demonstração de Resultado Abrangente - PDF - 169,6 KB</t>
+          <t>Balanço Financeiro; - 181,7 KB</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7_-_sesi_demonstracao_de_resultado_abrangente_2022.pdf</t>
+          <t>sesi_balanco_financeiro_2021.pdf</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/b6/37/b637b159-aad2-426f-b85b-c52bfb58a3f8/7_-_sesi_demonstracao_de_resultado_abrangente_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/1d/e8/1de8185f-6728-443f-8408-a13b505a2d4b/sesi_balanco_financeiro_2021.pdf</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -3044,7 +3044,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Notas Explicativas. - 1,5 MB</t>
+          <t>Demonstração das Variações Patrimoniais; - 181,6 KB</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3080,12 +3080,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8_-_sesi_notas_explicativas_2022.pdf</t>
+          <t>sesi_demonstracao_das_variacoes_patrimoniais_2021.pdf</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/03/62/0362087c-775a-45b5-9f5c-605b9bdad868/8_-_sesi_notas_explicativas_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/90/91/909125ba-e6e9-4f03-a4af-3c97d9124e15/sesi_demonstracao_das_variacoes_patrimoniais_2021.pdf</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -3099,7 +3099,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Balanço Patrimonial; - 178,3 KB</t>
+          <t>Demonstração de Fluxo de Caixa; - 172,8 KB</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>sesi_balanco_patrimonial_2021.pdf</t>
+          <t>sesi_demonstracao_de_fluxo_de_caixa_2021.pdf</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/6c/eb/6ceb4b76-b947-4461-bdf2-c66c0ec1625c/sesi_balanco_patrimonial_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/42/df/42df8d8a-a60b-4fbe-af46-65ca293a18b5/sesi_demonstracao_de_fluxo_de_caixa_2021.pdf</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3154,7 +3154,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Balanço Orçamentário; - 179,8 KB</t>
+          <t>Demonstração das Mutações do Patrimônio Líquido - 171,1 KB</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3190,12 +3190,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>sesi_balanco_orcamentario_2021.pdf</t>
+          <t>sesi__demonstracao_das_mutacoes_do_patrimonio_liquido_2021.pdf</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/96/2f/962fcc6f-95f6-47e5-af30-03806b938d82/sesi_balanco_orcamentario_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/8f/5d/8f5dff76-45bb-4978-8b4a-8588f6865088/sesi__demonstracao_das_mutacoes_do_patrimonio_liquido_2021.pdf</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3209,7 +3209,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Balanço Financeiro; - 181,7 KB</t>
+          <t>Demonstração de Resultado Abrangente - 170,7 KB</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>sesi_balanco_financeiro_2021.pdf</t>
+          <t>sesi_demonstracao_de_resultado_abrangente_2021.pdf</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/1d/e8/1de8185f-6728-443f-8408-a13b505a2d4b/sesi_balanco_financeiro_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/19/0d/190d5789-b1b2-4ac9-a112-a0e131a00974/sesi_demonstracao_de_resultado_abrangente_2021.pdf</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3264,7 +3264,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Demonstração das Variações Patrimoniais; - 181,6 KB</t>
+          <t>Notas Explicativas. - 891,4 KB</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3300,12 +3300,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>sesi_demonstracao_das_variacoes_patrimoniais_2021.pdf</t>
+          <t>sesi_notas_explicativas_as_demonstracoes_2021.pdf</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/90/91/909125ba-e6e9-4f03-a4af-3c97d9124e15/sesi_demonstracao_das_variacoes_patrimoniais_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/68/28/682854fe-8fac-4efb-8a15-60a0247bfc10/sesi_notas_explicativas_as_demonstracoes_2021.pdf</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -3319,7 +3319,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3334,18 +3334,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Índice — DEMONSTRAÇÕES CONTÁBEIS</t>
+          <t>Índice — GRATUIDADE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Demonstração de Fluxo de Caixa; - 172,8 KB</t>
+          <t>Metodologia de Apuração da Gratuidade Regulamentar - SESI 628,2 KB</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Transparência (índice) | DEMONSTRAÇÕES CONTÁBEIS</t>
+          <t>Transparência (índice) | GRATUIDADE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>sesi_demonstracao_de_fluxo_de_caixa_2021.pdf</t>
+          <t>link_sesi_gratuidade_fase_1_-_portal_da_industria_revisado_20190502.pdf</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/42/df/42df8d8a-a60b-4fbe-af46-65ca293a18b5/sesi_demonstracao_de_fluxo_de_caixa_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/c7/93/c79317e4-d221-4da5-a38c-42ef905ff003/link_sesi_gratuidade_fase_1_-_portal_da_industria_revisado_20190502.pdf</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3374,7 +3374,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3389,18 +3389,18 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Índice — DEMONSTRAÇÕES CONTÁBEIS</t>
+          <t>Índice — INTEGRIDADE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Demonstração das Mutações do Patrimônio Líquido - 171,1 KB</t>
+          <t>Código de Conduta Ética 3.6 Mb</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Transparência (índice) | DEMONSTRAÇÕES CONTÁBEIS</t>
+          <t>Transparência (índice) | INTEGRIDADE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>sesi__demonstracao_das_mutacoes_do_patrimonio_liquido_2021.pdf</t>
+          <t>codigo_de_conduta_etica.pdf</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/8f/5d/8f5dff76-45bb-4978-8b4a-8588f6865088/sesi__demonstracao_das_mutacoes_do_patrimonio_liquido_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/06/46/064648e0-eeb5-435b-b59d-1ad41c93ec5b/codigo_de_conduta_etica.pdf</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3429,7 +3429,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3444,18 +3444,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Índice — DEMONSTRAÇÕES CONTÁBEIS</t>
+          <t>Índice — INTEGRIDADE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Demonstração de Resultado Abrangente - 170,7 KB</t>
+          <t>2º Tri - 2026 1.0 Mb</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Transparência (índice) | DEMONSTRAÇÕES CONTÁBEIS</t>
+          <t>Transparência (índice) | INTEGRIDADE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>sesi_demonstracao_de_resultado_abrangente_2021.pdf</t>
+          <t>2026-07-24_normalizado_relatorio_sesi_-_2_tri_2026.pdf</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/19/0d/190d5789-b1b2-4ac9-a112-a0e131a00974/sesi_demonstracao_de_resultado_abrangente_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/26/d3/26d39375-14ba-431e-bbc5-230215c8b900/2026-07-24_normalizado_relatorio_sesi_-_2_tri_2026.pdf</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3484,7 +3484,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3499,18 +3499,18 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Índice — DEMONSTRAÇÕES CONTÁBEIS</t>
+          <t>Índice — INTEGRIDADE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Notas Explicativas. - 891,4 KB</t>
+          <t>2025 1.4 Mb</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Transparência (índice) | DEMONSTRAÇÕES CONTÁBEIS</t>
+          <t>Transparência (índice) | INTEGRIDADE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>sesi_notas_explicativas_as_demonstracoes_2021.pdf</t>
+          <t>2026-01-30_minuta_relatorio_de_controle_interno_sesi_2025_1.pdf</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/68/28/682854fe-8fac-4efb-8a15-60a0247bfc10/sesi_notas_explicativas_as_demonstracoes_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f5/29/f5292a47-ff53-4771-add1-ce83855f58c1/2026-01-30_minuta_relatorio_de_controle_interno_sesi_2025_1.pdf</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -3539,7 +3539,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3554,18 +3554,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Índice — GRATUIDADE</t>
+          <t>Índice — INTEGRIDADE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Metodologia de Apuração da Gratuidade Regulamentar - SESI 628,2 KB</t>
+          <t>2024 1.5 Mb</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Transparência (índice) | GRATUIDADE</t>
+          <t>Transparência (índice) | INTEGRIDADE</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>link_sesi_gratuidade_fase_1_-_portal_da_industria_revisado_20190502.pdf</t>
+          <t>2025-01-31_rci_sesi_2024_final.pdf</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/c7/93/c79317e4-d221-4da5-a38c-42ef905ff003/link_sesi_gratuidade_fase_1_-_portal_da_industria_revisado_20190502.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/61/3d/613d5e7b-69cc-49df-9b8d-7f9b2dc3a226/2025-01-31_rci_sesi_2024_final.pdf</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -3594,7 +3594,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Código de Conduta Ética 3.6 Mb</t>
+          <t>2023 5.7 Mb</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3630,12 +3630,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>codigo_de_conduta_etica.pdf</t>
+          <t>20240131_-_relatorio_de_controle_interno_sesi_-_4_tri_2023.pdf</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/06/46/064648e0-eeb5-435b-b59d-1ad41c93ec5b/codigo_de_conduta_etica.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/c9/b2/c9b22ab0-f911-45be-9a76-07e884034471/20240131_-_relatorio_de_controle_interno_sesi_-_4_tri_2023.pdf</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3649,7 +3649,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2º Tri - 2026 1.0 Mb</t>
+          <t>2022 5.6 Mb</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-24_normalizado_relatorio_sesi_-_2_tri_2026.pdf</t>
+          <t>sesi_dn__relatorio_de_controle_interno__4o_trimestre_2022.pdf</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/26/d3/26d39375-14ba-431e-bbc5-230215c8b900/2026-07-24_normalizado_relatorio_sesi_-_2_tri_2026.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/3f/da/3fdaba1d-5bdf-4bd9-9df1-de90ec570cbd/sesi_dn__relatorio_de_controle_interno__4o_trimestre_2022.pdf</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3704,7 +3704,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025 1.4 Mb</t>
+          <t>2021 1.3 Mb</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3740,12 +3740,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-01-30_minuta_relatorio_de_controle_interno_sesi_2025_1.pdf</t>
+          <t>relatorio_de_controle_interno_sesi_-_4_trimestre_2021.pdf</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f5/29/f5292a47-ff53-4771-add1-ce83855f58c1/2026-01-30_minuta_relatorio_de_controle_interno_sesi_2025_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/dd/97/dd978739-96f5-409f-83ca-cf7deba34b89/relatorio_de_controle_interno_sesi_-_4_trimestre_2021.pdf</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3759,7 +3759,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2024 1.5 Mb</t>
+          <t>2º Tri - 2026 1.2 Mb</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2025-01-31_rci_sesi_2024_final.pdf</t>
+          <t>relatorio_2o_tri_2026_sesi.pdf</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/61/3d/613d5e7b-69cc-49df-9b8d-7f9b2dc3a226/2025-01-31_rci_sesi_2024_final.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/5d/e1/5de1550e-9027-41fe-ab70-9a7a60ec8cde/relatorio_2o_tri_2026_sesi.pdf</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -3814,7 +3814,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2023 5.7 Mb</t>
+          <t>2025 1.3 Mb</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3850,12 +3850,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>20240131_-_relatorio_de_controle_interno_sesi_-_4_tri_2023.pdf</t>
+          <t>relatorio_monitoramento_sesi_2025_1.pdf</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/c9/b2/c9b22ab0-f911-45be-9a76-07e884034471/20240131_-_relatorio_de_controle_interno_sesi_-_4_tri_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/95/e1/95e18b7a-32b7-46e1-9fac-3c68bd38771e/relatorio_monitoramento_sesi_2025_1.pdf</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -3869,7 +3869,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2022 5.6 Mb</t>
+          <t>2024 6.3 Mb</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>sesi_dn__relatorio_de_controle_interno__4o_trimestre_2022.pdf</t>
+          <t>relatorio_de_monitoramento_das_atividades_dos_canais_de_acesso_a_informacao_sesi_2024.pdf</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/3f/da/3fdaba1d-5bdf-4bd9-9df1-de90ec570cbd/sesi_dn__relatorio_de_controle_interno__4o_trimestre_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/3e/e6/3ee6dde4-382c-4b86-bbda-a422446e13af/relatorio_de_monitoramento_das_atividades_dos_canais_de_acesso_a_informacao_sesi_2024.pdf</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3924,7 +3924,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2021 1.3 Mb</t>
+          <t>2023 1.7 Mb</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>relatorio_de_controle_interno_sesi_-_4_trimestre_2021.pdf</t>
+          <t>relatorio_canais_de_manifestacao_2023_-_sesi.pdf</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/dd/97/dd978739-96f5-409f-83ca-cf7deba34b89/relatorio_de_controle_interno_sesi_-_4_trimestre_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/3a/2c/3a2c199d-f8e2-493b-8ede-bd0a6f31f6c9/relatorio_canais_de_manifestacao_2023_-_sesi.pdf</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -3979,7 +3979,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2º Tri - 2026 1.2 Mb</t>
+          <t>2022 2.4 Mb</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>relatorio_2o_tri_2026_sesi.pdf</t>
+          <t>rel_monit_atividades_canais_de_acesso_2022__sesi-dn_vf.pdf</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/5d/e1/5de1550e-9027-41fe-ab70-9a7a60ec8cde/relatorio_2o_tri_2026_sesi.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/b1/d3/b1d31196-082d-4143-bf65-5dd451b1f40b/rel_monit_atividades_canais_de_acesso_2022__sesi-dn_vf.pdf</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -4034,7 +4034,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025 1.3 Mb</t>
+          <t>2025 380 Kb</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>relatorio_monitoramento_sesi_2025_1.pdf</t>
+          <t>dashboard_ouvidoria_-_site_transparencia_sesi_30-01-2026.pdf</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/95/e1/95e18b7a-32b7-46e1-9fac-3c68bd38771e/relatorio_monitoramento_sesi_2025_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/23/24/2324f64c-c6f9-471a-ac93-79bd4dfb269b/dashboard_ouvidoria_-_site_transparencia_sesi_30-01-2026.pdf</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -4089,7 +4089,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2024 6.3 Mb</t>
+          <t>2024 303 Kb</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>relatorio_de_monitoramento_das_atividades_dos_canais_de_acesso_a_informacao_sesi_2024.pdf</t>
+          <t>demonstrativo_consolidado_ouvidoria_sesi_dn_2024-_pdf_1.pdf</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/3e/e6/3ee6dde4-382c-4b86-bbda-a422446e13af/relatorio_de_monitoramento_das_atividades_dos_canais_de_acesso_a_informacao_sesi_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/da/3f/da3fb4de-b6ac-498f-908d-232855ec0cec/demonstrativo_consolidado_ouvidoria_sesi_dn_2024-_pdf_1.pdf</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -4144,7 +4144,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2023 1.7 Mb</t>
+          <t>2023 586 Kb</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>relatorio_canais_de_manifestacao_2023_-_sesi.pdf</t>
+          <t>demonstrativo_consolidado_ouvidoria_2023_sesi_v2.pdf</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/3a/2c/3a2c199d-f8e2-493b-8ede-bd0a6f31f6c9/relatorio_canais_de_manifestacao_2023_-_sesi.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/48/4a/484a294f-c25f-4774-a0c1-7a5999169849/demonstrativo_consolidado_ouvidoria_2023_sesi_v2.pdf</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -4199,7 +4199,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2022 2.4 Mb</t>
+          <t>2022 303 Kb</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>rel_monit_atividades_canais_de_acesso_2022__sesi-dn_vf.pdf</t>
+          <t>demonstrativo_consolidado_ouvidoria_sesi-dn-2022_vf_2022.pdf</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/b1/d3/b1d31196-082d-4143-bf65-5dd451b1f40b/rel_monit_atividades_canais_de_acesso_2022__sesi-dn_vf.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/95/4f/954f7607-4f1a-4911-aef1-7d2173ec1521/demonstrativo_consolidado_ouvidoria_sesi-dn-2022_vf_2022.pdf</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -4254,7 +4254,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025 380 Kb</t>
+          <t>2021 122 Kb</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -4290,12 +4290,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>dashboard_ouvidoria_-_site_transparencia_sesi_30-01-2026.pdf</t>
+          <t>demonstrativo_sesi-dn_2021_v3_31012022_1.pdf</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/23/24/2324f64c-c6f9-471a-ac93-79bd4dfb269b/dashboard_ouvidoria_-_site_transparencia_sesi_30-01-2026.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/23/84/2384e16f-11f3-4611-ab20-44c8f42dbffb/demonstrativo_sesi-dn_2021_v3_31012022_1.pdf</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4309,7 +4309,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2024 303 Kb</t>
+          <t>2025 263 Kb</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -4345,12 +4345,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>demonstrativo_consolidado_ouvidoria_sesi_dn_2024-_pdf_1.pdf</t>
+          <t>sesi_resultados_do_sac_em_2025_v2.pdf</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/da/3f/da3fb4de-b6ac-498f-908d-232855ec0cec/demonstrativo_consolidado_ouvidoria_sesi_dn_2024-_pdf_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/bb/4c/bb4c6dcb-2d45-46f6-87db-2d8f16c45991/sesi_resultados_do_sac_em_2025_v2.pdf</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4364,7 +4364,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2023 586 Kb</t>
+          <t>2024 149 Kb</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>demonstrativo_consolidado_ouvidoria_2023_sesi_v2.pdf</t>
+          <t>sesi_resultados_do_sac_em_2024.pdf</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/48/4a/484a294f-c25f-4774-a0c1-7a5999169849/demonstrativo_consolidado_ouvidoria_2023_sesi_v2.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/6d/8f/6d8f2b00-8b3f-46bb-a42c-d5f53bbee48d/sesi_resultados_do_sac_em_2024.pdf</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4419,7 +4419,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2022 303 Kb</t>
+          <t>2023 122 Kb</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>demonstrativo_consolidado_ouvidoria_sesi-dn-2022_vf_2022.pdf</t>
+          <t>transparencia_sesi__resultados_do_sac_em_2023.pdf</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/95/4f/954f7607-4f1a-4911-aef1-7d2173ec1521/demonstrativo_consolidado_ouvidoria_sesi-dn-2022_vf_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/9a/2c/9a2c246d-cb63-4286-aed3-aa40c5c51aa8/transparencia_sesi__resultados_do_sac_em_2023.pdf</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4474,7 +4474,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2021 122 Kb</t>
+          <t>2022 94 Kb</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>demonstrativo_sesi-dn_2021_v3_31012022_1.pdf</t>
+          <t>demonstrativo_de_resultados_dos_canais_de_atendimento_sesi_2022.pdf</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/23/84/2384e16f-11f3-4611-ab20-44c8f42dbffb/demonstrativo_sesi-dn_2021_v3_31012022_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/3e/22/3e2282e2-8b0b-4a35-bdb4-697a7e5501b9/demonstrativo_de_resultados_dos_canais_de_atendimento_sesi_2022.pdf</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4529,7 +4529,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025 263 Kb</t>
+          <t>2021 183 Kb</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>sesi_resultados_do_sac_em_2025_v2.pdf</t>
+          <t>demonstrativo_consolidado_de_atendimentos_do_sac_sesi_2021_final.pdf</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/bb/4c/bb4c6dcb-2d45-46f6-87db-2d8f16c45991/sesi_resultados_do_sac_em_2025_v2.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/b6/31/b6313381-ce2b-4bf6-9a3b-85af2c76cf48/demonstrativo_consolidado_de_atendimentos_do_sac_sesi_2021_final.pdf</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4584,7 +4584,7 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4599,18 +4599,18 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Índice — INTEGRIDADE</t>
+          <t>Índice — ORÇAMENTO E EXECUÇÃO ORÇAMENTÁRIA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2024 149 Kb</t>
+          <t>Orçamento Retificado Aprovado 2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Transparência (índice) | INTEGRIDADE</t>
+          <t>Transparência (índice) | ORÇAMENTO E EXECUÇÃO ORÇAMENTÁRIA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>sesi_resultados_do_sac_em_2024.pdf</t>
+          <t>sesi_dn_-_orcamento_retificado_2026.pdf</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/6d/8f/6d8f2b00-8b3f-46bb-a42c-d5f53bbee48d/sesi_resultados_do_sac_em_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/78/84/788474a3-d26b-4065-a18d-130ac32cf2fb/sesi_dn_-_orcamento_retificado_2026.pdf</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4639,7 +4639,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4654,18 +4654,18 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Índice — INTEGRIDADE</t>
+          <t>Índice — ORÇAMENTO E EXECUÇÃO ORÇAMENTÁRIA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2023 122 Kb</t>
+          <t>Execução Orçamentária do Departamento Nacional 2019</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Transparência (índice) | INTEGRIDADE</t>
+          <t>Transparência (índice) | ORÇAMENTO E EXECUÇÃO ORÇAMENTÁRIA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>transparencia_sesi__resultados_do_sac_em_2023.pdf</t>
+          <t>execucao_orcamentaria_2019_sesi_acess.pdf</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/9a/2c/9a2c246d-cb63-4286-aed3-aa40c5c51aa8/transparencia_sesi__resultados_do_sac_em_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/41/96/419665b4-e05d-4ffc-9ae7-e3bfb3a33319/execucao_orcamentaria_2019_sesi_acess.pdf</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4694,7 +4694,7 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4709,18 +4709,18 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Índice — INTEGRIDADE</t>
+          <t>Índice — ORÇAMENTO DO SISTEMA SESI</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2022 94 Kb</t>
+          <t>Orçamento anual aprovado do Sistema SESI para 2026 2.5 Mb</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Transparência (índice) | INTEGRIDADE</t>
+          <t>Transparência (índice) | ORÇAMENTO DO SISTEMA SESI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>demonstrativo_de_resultados_dos_canais_de_atendimento_sesi_2022.pdf</t>
+          <t>sistema_sesi_-_orcamento_inicial__2026_1.pdf</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/3e/22/3e2282e2-8b0b-4a35-bdb4-697a7e5501b9/demonstrativo_de_resultados_dos_canais_de_atendimento_sesi_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/d3/3d/d33d6b5e-ab35-4785-92ac-f43cb5024cd3/sistema_sesi_-_orcamento_inicial__2026_1.pdf</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4749,7 +4749,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4764,18 +4764,18 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Índice — INTEGRIDADE</t>
+          <t>Índice — ORÇAMENTO DO SISTEMA SESI</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2021 183 Kb</t>
+          <t>Orçamento anual aprovado do Sistema SESI para 2025 2.5 Mb</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Transparência (índice) | INTEGRIDADE</t>
+          <t>Transparência (índice) | ORÇAMENTO DO SISTEMA SESI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>demonstrativo_consolidado_de_atendimentos_do_sac_sesi_2021_final.pdf</t>
+          <t>relatprevisaoorcamentaria_2025.pdf</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/b6/31/b6313381-ce2b-4bf6-9a3b-85af2c76cf48/demonstrativo_consolidado_de_atendimentos_do_sac_sesi_2021_final.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/d7/72/d7723bd6-c32f-45c3-bc55-63ab27990fe2/relatprevisaoorcamentaria_2025.pdf</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4804,7 +4804,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4819,18 +4819,18 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Índice — ORÇAMENTO E EXECUÇÃO ORÇAMENTÁRIA</t>
+          <t>Índice — ORÇAMENTO DO SISTEMA SESI</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Orçamento Retificado Aprovado 2026</t>
+          <t>Orçamento anual aprovado do Sistema SESI para 2024 172 Kb</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Transparência (índice) | ORÇAMENTO E EXECUÇÃO ORÇAMENTÁRIA</t>
+          <t>Transparência (índice) | ORÇAMENTO DO SISTEMA SESI</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>sesi_dn_-_orcamento_retificado_2026.pdf</t>
+          <t>sesi_sistema_-_orcamento_inicial_2024.pdf</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/78/84/788474a3-d26b-4065-a18d-130ac32cf2fb/sesi_dn_-_orcamento_retificado_2026.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/8c/9c/8c9ca955-6a25-4316-b766-d72b18c43c3b/sesi_sistema_-_orcamento_inicial_2024.pdf</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4859,7 +4859,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4874,18 +4874,18 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Índice — ORÇAMENTO E EXECUÇÃO ORÇAMENTÁRIA</t>
+          <t>Índice — ORÇAMENTO DO SISTEMA SESI</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Execução Orçamentária do Departamento Nacional 2019</t>
+          <t>Orçamento anual aprovado do Sistema SESI para 2023 167 Kb</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Transparência (índice) | ORÇAMENTO E EXECUÇÃO ORÇAMENTÁRIA</t>
+          <t>Transparência (índice) | ORÇAMENTO DO SISTEMA SESI</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>execucao_orcamentaria_2019_sesi_acess.pdf</t>
+          <t>2023_orcamento_aprovado_do_sistema_sesi_para_2023.pdf</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/41/96/419665b4-e05d-4ffc-9ae7-e3bfb3a33319/execucao_orcamentaria_2019_sesi_acess.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/3c/25/3c251031-7a71-4e6d-acec-ccd92862a2b2/2023_orcamento_aprovado_do_sistema_sesi_para_2023.pdf</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -4914,7 +4914,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Orçamento anual aprovado do Sistema SESI para 2026 2.5 Mb</t>
+          <t>Orçamento anual aprovado do Sistema SESI para 2022 167 Kb</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>sistema_sesi_-_orcamento_inicial__2026_1.pdf</t>
+          <t>2022_orcamento_aprovado_do_sistema_sesi_para_2022.pdf</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/d3/3d/d33d6b5e-ab35-4785-92ac-f43cb5024cd3/sistema_sesi_-_orcamento_inicial__2026_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/92/c4/92c40fbd-10ef-462a-a14c-1867946bf1f8/2022_orcamento_aprovado_do_sistema_sesi_para_2022.pdf</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -4969,7 +4969,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Orçamento anual aprovado do Sistema SESI para 2025 2.5 Mb</t>
+          <t>Orçamento anual aprovado do Sistema SESI para 2021 453 Kb</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -5005,12 +5005,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>relatprevisaoorcamentaria_2025.pdf</t>
+          <t>2021_orcamento_aprovado_do_sistema_sesi_para_2021.pdf</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/d7/72/d7723bd6-c32f-45c3-bc55-63ab27990fe2/relatprevisaoorcamentaria_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/e8/b6/e8b61321-0117-4579-85a2-c13a25bff2c5/2021_orcamento_aprovado_do_sistema_sesi_para_2021.pdf</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -5024,7 +5024,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Orçamento anual aprovado do Sistema SESI para 2024 172 Kb</t>
+          <t>Orçamento Suplementado Aprovado do Sistema SESI para 2022 191 Kb</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>sesi_sistema_-_orcamento_inicial_2024.pdf</t>
+          <t>2022_orcamento_suplementado_aprovado_do_sistema_sesi_para_2022.pdf</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/8c/9c/8c9ca955-6a25-4316-b766-d72b18c43c3b/sesi_sistema_-_orcamento_inicial_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f2/7c/f27cb730-017d-40b8-a958-0d0464697693/2022_orcamento_suplementado_aprovado_do_sistema_sesi_para_2022.pdf</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -5079,7 +5079,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Orçamento anual aprovado do Sistema SESI para 2023 167 Kb</t>
+          <t>Orçamento Suplementado Aprovado do Sistema SESI para 2021 171 Kb</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -5115,12 +5115,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2023_orcamento_aprovado_do_sistema_sesi_para_2023.pdf</t>
+          <t>2021_orcamento_suplementado_aprovado_do_sistema_sesi_para_2021.pdf</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/3c/25/3c251031-7a71-4e6d-acec-ccd92862a2b2/2023_orcamento_aprovado_do_sistema_sesi_para_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/3a/51/3a5151cf-fc4e-4635-b22d-58176c4bc376/2021_orcamento_suplementado_aprovado_do_sistema_sesi_para_2021.pdf</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -5134,7 +5134,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Orçamento anual aprovado do Sistema SESI para 2022 167 Kb</t>
+          <t>Orçamento Retificado Aprovado do Sistema SESI para 2026 179 Kb</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2022_orcamento_aprovado_do_sistema_sesi_para_2022.pdf</t>
+          <t>sesi_sistema_-_orcamento_retificado_2026.pdf</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/92/c4/92c40fbd-10ef-462a-a14c-1867946bf1f8/2022_orcamento_aprovado_do_sistema_sesi_para_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/dd/dc/dddc2230-73da-4942-8a75-61211658f522/sesi_sistema_-_orcamento_retificado_2026.pdf</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -5189,7 +5189,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Orçamento anual aprovado do Sistema SESI para 2021 453 Kb</t>
+          <t>Orçamento Retificado Aprovado do Sistema SESI para 2025 2.5 Mb</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -5225,12 +5225,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2021_orcamento_aprovado_do_sistema_sesi_para_2021.pdf</t>
+          <t>orcamento_retificado_aprovado_do_sistema_sesi_para_2025.pdf</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/e8/b6/e8b61321-0117-4579-85a2-c13a25bff2c5/2021_orcamento_aprovado_do_sistema_sesi_para_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/48/01/4801f5f0-6632-47b2-acd9-e11fee73030e/orcamento_retificado_aprovado_do_sistema_sesi_para_2025.pdf</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -5244,7 +5244,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Orçamento Suplementado Aprovado do Sistema SESI para 2022 191 Kb</t>
+          <t>Orçamento Retificado Aprovado do Sistema SESI para 2024 182 Kb</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2022_orcamento_suplementado_aprovado_do_sistema_sesi_para_2022.pdf</t>
+          <t>sesi_sistema_-_orcamento_retificado_2024.pdf</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f2/7c/f27cb730-017d-40b8-a958-0d0464697693/2022_orcamento_suplementado_aprovado_do_sistema_sesi_para_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/c1/58/c158e211-27cb-4547-9229-a9ef64128a34/sesi_sistema_-_orcamento_retificado_2024.pdf</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -5299,7 +5299,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Orçamento Suplementado Aprovado do Sistema SESI para 2021 171 Kb</t>
+          <t>Orçamento Retificado Aprovado do Sistema SESI para 2023 180 Kb</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2021_orcamento_suplementado_aprovado_do_sistema_sesi_para_2021.pdf</t>
+          <t>sesi_sistema_-_orcamento_retificado_2023.pdf</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/3a/51/3a5151cf-fc4e-4635-b22d-58176c4bc376/2021_orcamento_suplementado_aprovado_do_sistema_sesi_para_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/c2/f6/c2f64ced-c65c-4d59-8f6a-c5cd491649f0/sesi_sistema_-_orcamento_retificado_2023.pdf</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -5354,7 +5354,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Orçamento Retificado Aprovado do Sistema SESI para 2026 179 Kb</t>
+          <t>Portaria nº 1.114 do MDS, de 08.10.2025 - Aprova a retificação do Sistema SESI para 2025 424 Kb</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>sesi_sistema_-_orcamento_retificado_2026.pdf</t>
+          <t>portaria_mds_no_1114_de_08_de_outubro_de_2025_-_reformulacao.pdf</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/dd/dc/dddc2230-73da-4942-8a75-61211658f522/sesi_sistema_-_orcamento_retificado_2026.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/13/0e/130e201d-dd65-4c61-91a0-6f48a9077712/portaria_mds_no_1114_de_08_de_outubro_de_2025_-_reformulacao.pdf</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -5409,7 +5409,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Orçamento Retificado Aprovado do Sistema SESI para 2025 2.5 Mb</t>
+          <t>Portaria nº 1047 do MDS, de 30.12.2024 - Aprova o orçamento do Sistema SESI para o exercício de 2025 575 Kb</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -5445,12 +5445,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>orcamento_retificado_aprovado_do_sistema_sesi_para_2025.pdf</t>
+          <t>portaria_mds_no_1047_de_30_de_dezembro_de_2024_-_portaria_mds_no_1047_de_30_de_dezembro_de_2024_-_dou_-_imprensa_nacional.pdf</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/48/01/4801f5f0-6632-47b2-acd9-e11fee73030e/orcamento_retificado_aprovado_do_sistema_sesi_para_2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/43/bf/43bf2f4a-5468-4dca-8b09-d517f90a4cd7/portaria_mds_no_1047_de_30_de_dezembro_de_2024_-_portaria_mds_no_1047_de_30_de_dezembro_de_2024_-_dou_-_imprensa_nacional.pdf</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -5464,7 +5464,7 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Orçamento Retificado Aprovado do Sistema SESI para 2024 182 Kb</t>
+          <t>Portaria nº 1.024 do MDS, de 23.10.2024 - Aprova a retificação do Sistema SESI para 2024 733 Kb</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>sesi_sistema_-_orcamento_retificado_2024.pdf</t>
+          <t>portaria_mds_no_1024_de_23_de_outubro_de_2024_-aprova_a_retificacao_do_sistema_sesi_para_2024.pdf</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/c1/58/c158e211-27cb-4547-9229-a9ef64128a34/sesi_sistema_-_orcamento_retificado_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/87/7f/877fbba7-e2e8-4eff-8b67-9a84087a06d3/portaria_mds_no_1024_de_23_de_outubro_de_2024_-aprova_a_retificacao_do_sistema_sesi_para_2024.pdf</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5519,7 +5519,7 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Orçamento Retificado Aprovado do Sistema SESI para 2023 180 Kb</t>
+          <t>Portaria nº 947 do MC, de 21.12.2023 - Portarias de aprovação das propostas orçamentárias 2024 114 Kb</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>sesi_sistema_-_orcamento_retificado_2023.pdf</t>
+          <t>portaria_mds_no_947_de_21_de_dezembro_de_2023_-_sesi.pdf</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/c2/f6/c2f64ced-c65c-4d59-8f6a-c5cd491649f0/sesi_sistema_-_orcamento_retificado_2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/86/03/860343ba-1e2d-4b67-9dd7-c12184128242/portaria_mds_no_947_de_21_de_dezembro_de_2023_-_sesi.pdf</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -5574,7 +5574,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Portaria nº 1.114 do MDS, de 08.10.2025 - Aprova a retificação do Sistema SESI para 2025 424 Kb</t>
+          <t>Portaria nº 915 do MDS, de 13.09.2023 - Aprova a retificação do Sistema SESI para 2023 496 Kb</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>portaria_mds_no_1114_de_08_de_outubro_de_2025_-_reformulacao.pdf</t>
+          <t>portaria_mds_no_915_de_13_de_setembro_de_2023_-_portaria_mds_no_915_de_13_d.pdf</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/13/0e/130e201d-dd65-4c61-91a0-6f48a9077712/portaria_mds_no_1114_de_08_de_outubro_de_2025_-_reformulacao.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/b0/11/b011aa5d-be01-49db-b9d1-6f7c8067e69c/portaria_mds_no_915_de_13_de_setembro_de_2023_-_portaria_mds_no_915_de_13_d.pdf</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5629,7 +5629,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Portaria nº 1047 do MDS, de 30.12.2024 - Aprova o orçamento do Sistema SESI para o exercício de 2025 575 Kb</t>
+          <t>Portaria nº 850 do MC, de 29.12.2022 - Portarias de aprovação das propostas orçamentárias 2023 456 Kb</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -5665,12 +5665,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>portaria_mds_no_1047_de_30_de_dezembro_de_2024_-_portaria_mds_no_1047_de_30_de_dezembro_de_2024_-_dou_-_imprensa_nacional.pdf</t>
+          <t>2023_portaria_no_850_de_29122022_-_aprova_orcamentaria_anual_sistema_sesi.pdf</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/43/bf/43bf2f4a-5468-4dca-8b09-d517f90a4cd7/portaria_mds_no_1047_de_30_de_dezembro_de_2024_-_portaria_mds_no_1047_de_30_de_dezembro_de_2024_-_dou_-_imprensa_nacional.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/fe/ff/feffdf09-3f53-4117-8574-2edd99680261/2023_portaria_no_850_de_29122022_-_aprova_orcamentaria_anual_sistema_sesi.pdf</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -5684,7 +5684,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Portaria nº 1.024 do MDS, de 23.10.2024 - Aprova a retificação do Sistema SESI para 2024 733 Kb</t>
+          <t>Portaria nº 828 do MC, de 31.10.2022 - Aprova a Suplementação Anual do Sistema SESI para 2022 434 Kb</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -5720,12 +5720,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>portaria_mds_no_1024_de_23_de_outubro_de_2024_-aprova_a_retificacao_do_sistema_sesi_para_2024.pdf</t>
+          <t>2022_portaria_no_829_de_31102022_-_aprova_supl_anual_sistema_sesi_2022.pdf</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/87/7f/877fbba7-e2e8-4eff-8b67-9a84087a06d3/portaria_mds_no_1024_de_23_de_outubro_de_2024_-aprova_a_retificacao_do_sistema_sesi_para_2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/93/ed/93ed3f57-8032-4cfd-bde9-cc122ada92ca/2022_portaria_no_829_de_31102022_-_aprova_supl_anual_sistema_sesi_2022.pdf</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5739,7 +5739,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Portaria nº 947 do MC, de 21.12.2023 - Portarias de aprovação das propostas orçamentárias 2024 114 Kb</t>
+          <t>Portaria nº 732 do MC, de 28.12.2021 - Portarias de aprovação das propostas orçamentárias 2022 434 Kb</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -5775,12 +5775,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>portaria_mds_no_947_de_21_de_dezembro_de_2023_-_sesi.pdf</t>
+          <t>2022_portaria_no_732_de_28122021_-_aprova_orcamentari_anual_sistema_sesi_2022.pdf</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/86/03/860343ba-1e2d-4b67-9dd7-c12184128242/portaria_mds_no_947_de_21_de_dezembro_de_2023_-_sesi.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/8b/40/8b40a420-4f27-49dd-b3c2-2da1d2fd2787/2022_portaria_no_732_de_28122021_-_aprova_orcamentari_anual_sistema_sesi_2022.pdf</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -5794,7 +5794,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Portaria nº 915 do MDS, de 13.09.2023 - Aprova a retificação do Sistema SESI para 2023 496 Kb</t>
+          <t>Portaria nº 703 do MC, de 29.10.2021 - Portarias de aprovação das propostas orçamentárias 2021 427 Kb</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -5830,12 +5830,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>portaria_mds_no_915_de_13_de_setembro_de_2023_-_portaria_mds_no_915_de_13_d.pdf</t>
+          <t>2021_portaria_no_703_de_29102021_-_aprova_supl_anual_sistema_sesi_2021.pdf</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/b0/11/b011aa5d-be01-49db-b9d1-6f7c8067e69c/portaria_mds_no_915_de_13_de_setembro_de_2023_-_portaria_mds_no_915_de_13_d.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/41/3e/413e2aea-b382-411b-b429-a675985a56be/2021_portaria_no_703_de_29102021_-_aprova_supl_anual_sistema_sesi_2021.pdf</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -5849,7 +5849,7 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Portaria nº 850 do MC, de 29.12.2022 - Portarias de aprovação das propostas orçamentárias 2023 456 Kb</t>
+          <t>Portaria nº 563 do MC, de 17.12.2020 - Portarias de aprovação das propostas orçamentárias 2021 101 Kb</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2023_portaria_no_850_de_29122022_-_aprova_orcamentaria_anual_sistema_sesi.pdf</t>
+          <t>2021_portaria_no_563_de_17122020_-_aprova_orcamentaria_anual_sistema_sesi_2021.pdf</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/fe/ff/feffdf09-3f53-4117-8574-2edd99680261/2023_portaria_no_850_de_29122022_-_aprova_orcamentaria_anual_sistema_sesi.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/74/23/74239939-cf7d-4853-8405-0646efb20e86/2021_portaria_no_563_de_17122020_-_aprova_orcamentaria_anual_sistema_sesi_2021.pdf</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -5904,7 +5904,7 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5919,18 +5919,18 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Índice — ORÇAMENTO DO SISTEMA SESI</t>
+          <t>Licitações / Processos de Seleção</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Portaria nº 828 do MC, de 31.10.2022 - Aprova a Suplementação Anual do Sistema SESI para 2022 434 Kb</t>
+          <t>Licitações e Editais (PDF) 2022 282 Kb</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Transparência (índice) | ORÇAMENTO DO SISTEMA SESI</t>
+          <t>Licitações / Processos de Seleção</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2022_portaria_no_829_de_31102022_-_aprova_supl_anual_sistema_sesi_2022.pdf</t>
+          <t>20230210_plano_de_contingencia_licitacoes_sesi_dn_2022.pdf</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/93/ed/93ed3f57-8032-4cfd-bde9-cc122ada92ca/2022_portaria_no_829_de_31102022_-_aprova_supl_anual_sistema_sesi_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/e4/5e/e45e6a36-fb5c-4403-bd05-7b435b96cefc/20230210_plano_de_contingencia_licitacoes_sesi_dn_2022.pdf</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -5959,7 +5959,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -5974,18 +5974,18 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Índice — ORÇAMENTO DO SISTEMA SESI</t>
+          <t>Licitações / Processos de Seleção</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Portaria nº 732 do MC, de 28.12.2021 - Portarias de aprovação das propostas orçamentárias 2022 434 Kb</t>
+          <t>Licitações e Editais (PDF) 2021 159 Kb</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Transparência (índice) | ORÇAMENTO DO SISTEMA SESI</t>
+          <t>Licitações / Processos de Seleção</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2022_portaria_no_732_de_28122021_-_aprova_orcamentari_anual_sistema_sesi_2022.pdf</t>
+          <t>2021_pdf.pdf</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/8b/40/8b40a420-4f27-49dd-b3c2-2da1d2fd2787/2022_portaria_no_732_de_28122021_-_aprova_orcamentari_anual_sistema_sesi_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/3c/18/3c18a076-7d97-4f01-b331-830fcfeb9707/2021_pdf.pdf</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -6014,7 +6014,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6029,18 +6029,18 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Índice — ORÇAMENTO DO SISTEMA SESI</t>
+          <t>Processos de contratação</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Portaria nº 703 do MC, de 29.10.2021 - Portarias de aprovação das propostas orçamentárias 2021 427 Kb</t>
+          <t>CV 01/2021 - Projeto Escola SESI — Aviso de cancelamento -14/05/2021</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Transparência (índice) | ORÇAMENTO DO SISTEMA SESI</t>
+          <t>Processos de contratação | SESI | RLC Convite | Encerrado/Concluído | Outros Documentos</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2021_portaria_no_703_de_29102021_-_aprova_supl_anual_sistema_sesi_2021.pdf</t>
+          <t>dou_cv_1-2021_cancelamento__publicado_em_14052021.pdf</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/41/3e/413e2aea-b382-411b-b429-a675985a56be/2021_portaria_no_703_de_29102021_-_aprova_supl_anual_sistema_sesi_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/cb/58/cb5826bc-99d2-48bd-85e1-607bbe2c742b/dou_cv_1-2021_cancelamento__publicado_em_14052021.pdf</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -6069,7 +6069,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6084,18 +6084,18 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Índice — ORÇAMENTO DO SISTEMA SESI</t>
+          <t>Processos de contratação</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Portaria nº 563 do MC, de 17.12.2020 - Portarias de aprovação das propostas orçamentárias 2021 101 Kb</t>
+          <t>Edital CR 2/2021 - Reforma e Requalificação de uma Praça — Ata - 10-5-2021 - Habilitação</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Transparência (índice) | ORÇAMENTO DO SISTEMA SESI</t>
+          <t>Processos de contratação | SESI | RLC Concorrência | Encerrado/Concluído | Outros Documentos</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2021_portaria_no_563_de_17122020_-_aprova_orcamentaria_anual_sistema_sesi_2021.pdf</t>
+          <t>ata_cr_2-2021_-_reforma_praca_pouring.pdf</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/74/23/74239939-cf7d-4853-8405-0646efb20e86/2021_portaria_no_563_de_17122020_-_aprova_orcamentaria_anual_sistema_sesi_2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/98/c3/98c3476c-7b16-4427-8923-936512b4e5d9/ata_cr_2-2021_-_reforma_praca_pouring.pdf</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -6124,7 +6124,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6139,18 +6139,18 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Licitações / Processos de Seleção</t>
+          <t>Processos de contratação</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Licitações e Editais (PDF) 2022 282 Kb</t>
+          <t>Edital PP 28/2021 - Aquisição de mobiliário - Espaço Café — Esclarecimentos</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Licitações / Processos de Seleção</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Outros Documentos</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>20230210_plano_de_contingencia_licitacoes_sesi_dn_2022.pdf</t>
+          <t>esclarecimento_1.pdf</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/e4/5e/e45e6a36-fb5c-4403-bd05-7b435b96cefc/20230210_plano_de_contingencia_licitacoes_sesi_dn_2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/51/e2/51e20ebd-40eb-498a-ada0-df791bbb8d2c/esclarecimento_1.pdf</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -6179,7 +6179,7 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6194,18 +6194,18 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Licitações / Processos de Seleção</t>
+          <t>Processos de contratação</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Licitações e Editais (PDF) 2021 159 Kb</t>
+          <t>Edital PE 12/2022 - Licenças Microsoft Azure — Cancelamento</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Licitações / Processos de Seleção</t>
+          <t>Processos de contratação | CNI, SESI, SENAI, IEL | RLC Pregão Eletrônico | Encerrado/Concluído | Outros Documentos</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2021_pdf.pdf</t>
+          <t>dou_-_pe_12-2022_-_cancelamento_publicado_em_17022022.pdf</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/3c/18/3c18a076-7d97-4f01-b331-830fcfeb9707/2021_pdf.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/c4/04/c4040798-35f5-48ac-8c23-9bf9894578c4/dou_-_pe_12-2022_-_cancelamento_publicado_em_17022022.pdf</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -6234,7 +6234,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6254,13 +6254,13 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>CV 01/2021 - Projeto Escola SESI — Aviso de cancelamento -14/05/2021</t>
+          <t>PE 20/2022 - Contratação de Empresa de Limpeza e Conservação. — Aviso de cancelamento - 04/04/2022</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Convite | Encerrado/Concluído | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Outros Documentos</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>dou_cv_1-2021_cancelamento__publicado_em_14052021.pdf</t>
+          <t>dou_pe_20-2022_-_cancelamento_-_publicado_em_04042022.pdf</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/cb/58/cb5826bc-99d2-48bd-85e1-607bbe2c742b/dou_cv_1-2021_cancelamento__publicado_em_14052021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/0f/27/0f273612-8ac9-4c20-ab88-034b5432e1d2/dou_pe_20-2022_-_cancelamento_-_publicado_em_04042022.pdf</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -6289,7 +6289,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6309,13 +6309,13 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Edital CR 2/2021 - Reforma e Requalificação de uma Praça — Ata - 10-5-2021 - Habilitação</t>
+          <t>PE 21/2022 - ATENDIMENTO MÉDICO EMERGENCIAL — AVISO DE CANCELAMENTO.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Concorrência | Encerrado/Concluído | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Outros Documentos</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ata_cr_2-2021_-_reforma_praca_pouring.pdf</t>
+          <t>publicacao_dou_-_cancelamento.pdf</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/98/c3/98c3476c-7b16-4427-8923-936512b4e5d9/ata_cr_2-2021_-_reforma_praca_pouring.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/e7/c1/e7c1f473-9d37-44d2-8f68-c5ed1ebd7631/publicacao_dou_-_cancelamento.pdf</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -6344,7 +6344,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6364,13 +6364,13 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Edital PP 28/2021 - Aquisição de mobiliário - Espaço Café — Esclarecimentos</t>
+          <t>PE 14/2022 - Serviço de vigilância — Aviso de Cancelamento</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Outros Documentos</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>esclarecimento_1.pdf</t>
+          <t>publicacao_dou_-_cancelamento.pdf</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/51/e2/51e20ebd-40eb-498a-ada0-df791bbb8d2c/esclarecimento_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/34/07/3407a6a5-6272-4ccb-ac34-40ec6ad3c0ab/publicacao_dou_-_cancelamento.pdf</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -6399,7 +6399,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6419,13 +6419,13 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Edital PE 12/2022 - Licenças Microsoft Azure — Cancelamento</t>
+          <t>PE 24/2022 - Serviço de brigadista — Aviso de Cancelamento</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Processos de contratação | CNI, SESI, SENAI, IEL | RLC Pregão Eletrônico | Encerrado/Concluído | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Outros Documentos</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>dou_-_pe_12-2022_-_cancelamento_publicado_em_17022022.pdf</t>
+          <t>publicacao_dou_-_cancelamento.pdf</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/c4/04/c4040798-35f5-48ac-8c23-9bf9894578c4/dou_-_pe_12-2022_-_cancelamento_publicado_em_17022022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/b4/4d/b44d511c-e886-4cd1-a8f9-d660431413bb/publicacao_dou_-_cancelamento.pdf</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -6454,7 +6454,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>PE 20/2022 - Contratação de Empresa de Limpeza e Conservação. — Aviso de cancelamento - 04/04/2022</t>
+          <t>PE 31/2022 - Serviço de Limpeza — Aviso de Cancelamento</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -6490,12 +6490,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>dou_pe_20-2022_-_cancelamento_-_publicado_em_04042022.pdf</t>
+          <t>publicacao_dou_cancelamento_19-04.pdf</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/0f/27/0f273612-8ac9-4c20-ab88-034b5432e1d2/dou_pe_20-2022_-_cancelamento_-_publicado_em_04042022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/d6/94/d69451a1-c4aa-465b-8b66-1d38c3f69931/publicacao_dou_cancelamento_19-04.pdf</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6509,7 +6509,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6529,13 +6529,13 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>PE 21/2022 - ATENDIMENTO MÉDICO EMERGENCIAL — AVISO DE CANCELAMENTO.</t>
+          <t>Chamamento 067-2026 - Prestação de serviços técnicos de planejamento — Esclarecimento 1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2026-09-18 | Outros Documentos</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>publicacao_dou_-_cancelamento.pdf</t>
+          <t>esclarecimento_1.pdf</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/e7/c1/e7c1f473-9d37-44d2-8f68-c5ed1ebd7631/publicacao_dou_-_cancelamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/fe/62/fe622424-4535-420d-ad1a-95776fc4765b/esclarecimento_1.pdf</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -6564,7 +6564,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6584,13 +6584,13 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>PE 14/2022 - Serviço de vigilância — Aviso de Cancelamento</t>
+          <t>Chamamento 067-2026 - Prestação de serviços técnicos de planejamento — Esclarecimento 2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2026-09-18 | Outros Documentos</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>publicacao_dou_-_cancelamento.pdf</t>
+          <t>esclarecimento_2.pdf</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/34/07/3407a6a5-6272-4ccb-ac34-40ec6ad3c0ab/publicacao_dou_-_cancelamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/8f/f3/8ff3dd1a-b8b0-4f37-ab12-89488bf09d6e/esclarecimento_2.pdf</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -6619,7 +6619,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6639,13 +6639,13 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PE 24/2022 - Serviço de brigadista — Aviso de Cancelamento</t>
+          <t>CP 103/2025 - Atendimento e orientação ao público - SESI - LAB — CONTRATO DE PRESTAÇÃO DE SERVIÇOS CONDICOES GERAIS RCA</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2025-10-28 | Outros Documentos</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>publicacao_dou_-_cancelamento.pdf</t>
+          <t>contra1.pdf</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/b4/4d/b44d511c-e886-4cd1-a8f9-d660431413bb/publicacao_dou_-_cancelamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/b4/e1/b4e14f23-7f3a-44f1-acaa-a815ef974cf2/contra1.pdf</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6674,7 +6674,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6694,13 +6694,13 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PE 31/2022 - Serviço de Limpeza — Aviso de Cancelamento</t>
+          <t>CP 51/2025 - Elaboração de estudo sobre mercado educacional. — CANCELAMENTO</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-05-16 | Outros Documentos</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>publicacao_dou_cancelamento_19-04.pdf</t>
+          <t>despacho_cancelamentodocx_2.pdf</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/d6/94/d69451a1-c4aa-465b-8b66-1d38c3f69931/publicacao_dou_cancelamento_19-04.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/58/6c/586c574c-b051-475a-85eb-b929185cab92/despacho_cancelamentodocx_2.pdf</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6729,7 +6729,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6749,13 +6749,13 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Chamamento 067-2026 - Prestação de serviços técnicos de planejamento — Esclarecimento 1</t>
+          <t>CHAMAMENTO PUBLICO-27-2025 - Orientadores de Público SESI LAB — Aviso de Cancelamento</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2026-09-18 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-05-12 | Outros Documentos</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>esclarecimento_1.pdf</t>
+          <t>aviso_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/fe/62/fe622424-4535-420d-ad1a-95776fc4765b/esclarecimento_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/77/ad/77adb598-fed7-4d34-a849-42e73b7e9e90/aviso_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -6784,7 +6784,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6804,13 +6804,13 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Chamamento 067-2026 - Prestação de serviços técnicos de planejamento — Esclarecimento 2</t>
+          <t>Chamamento Público 30/202 - Fornecimento de Gêneros Alimentícios — Aviso de cancelamento</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2026-09-18 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-04-01 | Outros Documentos</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>esclarecimento_2.pdf</t>
+          <t>despacho_de_cancelamento_chamamento_no_302025.pdf</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/8f/f3/8ff3dd1a-b8b0-4f37-ab12-89488bf09d6e/esclarecimento_2.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/7b/07/7b07e0fc-a8ed-4fc4-8ec6-ee5cd8323601/despacho_de_cancelamento_chamamento_no_302025.pdf</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6839,7 +6839,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6859,13 +6859,13 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CP 103/2025 - Atendimento e orientação ao público - SESI - LAB — CONTRATO DE PRESTAÇÃO DE SERVIÇOS CONDICOES GERAIS RCA</t>
+          <t>CHAMAMENTO PUBLICO-19-2025 - Serviços Educacionais - SESI LAB — Parecer Final</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2025-10-28 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2025-03-27 | Outros Documentos</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>contra1.pdf</t>
+          <t>parecer_final.pdf</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/b4/e1/b4e14f23-7f3a-44f1-acaa-a815ef974cf2/contra1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/b4/78/b4787463-8790-4779-8268-63621708183e/parecer_final.pdf</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -6894,7 +6894,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6914,13 +6914,13 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CP 51/2025 - Elaboração de estudo sobre mercado educacional. — CANCELAMENTO</t>
+          <t>Chamamento Público 01/2025 - Material Didático EJA — Anexo IG - Guia Prático de Educação à Distância do SESI</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-05-16 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Fechada | Encerrado/Concluído | Abertura: 2025-03-20 | Outros Documentos</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>despacho_cancelamentodocx_2.pdf</t>
+          <t>anexo_ig_-_guia_pratico_de_educacao_a_distancia_do_sesi.pdf</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/58/6c/586c574c-b051-475a-85eb-b929185cab92/despacho_cancelamentodocx_2.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/60/df/60dfcd14-5b1c-49cd-8159-85044c9cfd97/anexo_ig_-_guia_pratico_de_educacao_a_distancia_do_sesi.pdf</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -6946,10 +6946,12 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
+      <c r="L118" t="n">
+        <v>47601.4</v>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -6969,13 +6971,13 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO-27-2025 - Orientadores de Público SESI LAB — Aviso de Cancelamento</t>
+          <t>Chamamento Público 01/2025 - Material Didático EJA — EJA_01 PROJETO DE CURSOS_A4_DIGITAL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-05-12 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Fechada | Encerrado/Concluído | Abertura: 2025-03-20 | Outros Documentos</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6985,12 +6987,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>aviso_de_cancelamento.pdf</t>
+          <t>eja_01_projeto_de_cursos_a4_digital.pdf</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/77/ad/77adb598-fed7-4d34-a849-42e73b7e9e90/aviso_de_cancelamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/3a/33/3a33571a-8aa7-4b06-a13a-341eb34c56af/eja_01_projeto_de_cursos_a4_digital.pdf</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -7004,7 +7006,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7024,13 +7026,13 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Chamamento Público 30/202 - Fornecimento de Gêneros Alimentícios — Aviso de cancelamento</t>
+          <t>Chamamento Público 01/2025 - Material Didático EJA — EJA_05 Metodologia de Reconhecimento de Saberes - Processos e Intrume</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-04-01 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Fechada | Encerrado/Concluído | Abertura: 2025-03-20 | Outros Documentos</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7040,12 +7042,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>despacho_de_cancelamento_chamamento_no_302025.pdf</t>
+          <t>eja_05_metodologia_de_reconhecimento_de_saberes_-_processos_e_intrumentos_miolo_a4_digital.pdf</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/7b/07/7b07e0fc-a8ed-4fc4-8ec6-ee5cd8323601/despacho_de_cancelamento_chamamento_no_302025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/0d/f0/0df0701c-dd40-49af-afd8-d4bb6e4b8099/eja_05_metodologia_de_reconhecimento_de_saberes_-_processos_e_intrumentos_miolo_a4_digital.pdf</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -7059,7 +7061,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7079,13 +7081,13 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO-19-2025 - Serviços Educacionais - SESI LAB — Parecer Final</t>
+          <t>CHAMAMENTO PUBLICO-23-2025 - construção de conteúdo — Parecer Final</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2025-03-27 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2025-03-13 | Outros Documentos</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7100,7 +7102,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/b4/78/b4787463-8790-4779-8268-63621708183e/parecer_final.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/38/a7/38a786c3-52e4-4433-81a0-d6de05a7a721/parecer_final.pdf</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -7114,7 +7116,7 @@
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7134,13 +7136,13 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Chamamento Público 01/2025 - Material Didático EJA — Anexo IG - Guia Prático de Educação à Distância do SESI</t>
+          <t>Chamamento Público 08/2025 - Software Gestão de Saúde e Segurança — Parecer Final</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Fechada | Encerrado/Concluído | Abertura: 2025-03-20 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2025-02-24 | Outros Documentos</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7150,12 +7152,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>anexo_ig_-_guia_pratico_de_educacao_a_distancia_do_sesi.pdf</t>
+          <t>chamamento_n_8-2025_-_make_or_buy.pdf</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/60/df/60dfcd14-5b1c-49cd-8159-85044c9cfd97/anexo_ig_-_guia_pratico_de_educacao_a_distancia_do_sesi.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/45/21/4521be94-2a40-4d3a-9a38-e2e729a5785e/chamamento_n_8-2025_-_make_or_buy.pdf</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -7166,12 +7168,10 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L122" t="n">
-        <v>47601.4</v>
-      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7191,13 +7191,13 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Chamamento Público 01/2025 - Material Didático EJA — EJA_01 PROJETO DE CURSOS_A4_DIGITAL</t>
+          <t>Chamamento Público nº 10/2025 - Elaboração de Conteúdo Redes Sociais — Aviso de Cancelamento</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Fechada | Encerrado/Concluído | Abertura: 2025-03-20 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-02-20 | Outros Documentos</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>eja_01_projeto_de_cursos_a4_digital.pdf</t>
+          <t>aviso_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/3a/33/3a33571a-8aa7-4b06-a13a-341eb34c56af/eja_01_projeto_de_cursos_a4_digital.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/6a/81/6a815f2e-5bd1-4135-8f0d-e266bdad211e/aviso_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -7226,7 +7226,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7246,13 +7246,13 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Chamamento Público 01/2025 - Material Didático EJA — EJA_05 Metodologia de Reconhecimento de Saberes - Processos e Intrume</t>
+          <t>CHAMAMENTO PÚBLICO-07-2025 - Locação de equipamentos. — Parecer Final</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Fechada | Encerrado/Concluído | Abertura: 2025-03-20 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2025-02-11 | Outros Documentos</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>eja_05_metodologia_de_reconhecimento_de_saberes_-_processos_e_intrumentos_miolo_a4_digital.pdf</t>
+          <t>chamamento_n_7-2025_-_locacao_equipamento_tidocx.pdf</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/0d/f0/0df0701c-dd40-49af-afd8-d4bb6e4b8099/eja_05_metodologia_de_reconhecimento_de_saberes_-_processos_e_intrumentos_miolo_a4_digital.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/80/58/80583bbe-b697-42c3-bfb6-d06926b43ba0/chamamento_n_7-2025_-_locacao_equipamento_tidocx.pdf</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -7281,7 +7281,7 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7301,13 +7301,13 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO-23-2025 - construção de conteúdo — Parecer Final</t>
+          <t>Chamamento Público nº 04/2025 - Contéudo de Midias Sociais SESILAB — Aviso de Cancelamento</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2025-03-13 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2025-02-07 | Outros Documentos</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7317,12 +7317,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>parecer_final.pdf</t>
+          <t>aviso_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/38/a7/38a786c3-52e4-4433-81a0-d6de05a7a721/parecer_final.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/54/55/54558956-2a91-497e-976e-cefb7c318087/aviso_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -7336,7 +7336,7 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7356,13 +7356,13 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Chamamento Público 08/2025 - Software Gestão de Saúde e Segurança — Parecer Final</t>
+          <t>CHAMAMENTO PUBLICO-90-2024 - Montagem VII Festival SESI de Educação — Parecer Final</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2025-02-24 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2025-01-14 | Outros Documentos</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>chamamento_n_8-2025_-_make_or_buy.pdf</t>
+          <t>parecer_final.pdf</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/45/21/4521be94-2a40-4d3a-9a38-e2e729a5785e/chamamento_n_8-2025_-_make_or_buy.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/6b/a4/6ba43270-aa75-42ff-8566-e3cb6fa2854b/parecer_final.pdf</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -7391,7 +7391,7 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7411,13 +7411,13 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 10/2025 - Elaboração de Conteúdo Redes Sociais — Aviso de Cancelamento</t>
+          <t>Chamamento Público nº 76/2024 - Serviço de Limpeza SESILAb — Esclarecimento nº 1</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-02-20 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-01-09 | Outros Documentos</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>aviso_de_cancelamento.pdf</t>
+          <t>esclarecimento_1.pdf</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/6a/81/6a815f2e-5bd1-4135-8f0d-e266bdad211e/aviso_de_cancelamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/39/72/3972186b-a205-46c2-a044-30b5c0adacf5/esclarecimento_1.pdf</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -7446,7 +7446,7 @@
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7466,13 +7466,13 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PÚBLICO-07-2025 - Locação de equipamentos. — Parecer Final</t>
+          <t>Chamamento Público nº 76/2024 - Serviço de Limpeza SESILAb — Aviso de Suspensão</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2025-02-11 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-01-09 | Outros Documentos</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>chamamento_n_7-2025_-_locacao_equipamento_tidocx.pdf</t>
+          <t>aviso_de_suspensao.pdf</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/80/58/80583bbe-b697-42c3-bfb6-d06926b43ba0/chamamento_n_7-2025_-_locacao_equipamento_tidocx.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/58/17/5817da8e-db21-4a84-8c84-36b8ff2f4b7a/aviso_de_suspensao.pdf</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -7501,7 +7501,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7521,13 +7521,13 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 04/2025 - Contéudo de Midias Sociais SESILAB — Aviso de Cancelamento</t>
+          <t>Chamamento Público nº 76/2024 - Serviço de Limpeza SESILAb — Comunicado de Recesso 2024-2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2025-02-07 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-01-09 | Outros Documentos</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>aviso_de_cancelamento.pdf</t>
+          <t>comunicado_recesso_2024-2025.pdf</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/54/55/54558956-2a91-497e-976e-cefb7c318087/aviso_de_cancelamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/86/4c/864c9059-d302-4dc8-a0b3-14ac10431b10/comunicado_recesso_2024-2025.pdf</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -7556,7 +7556,7 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7576,13 +7576,13 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO-90-2024 - Montagem VII Festival SESI de Educação — Parecer Final</t>
+          <t>Chamamento Público nº 76/2024 - Serviço de Limpeza SESILAb — Errata - Modelo de Proposta</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2025-01-14 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-01-09 | Outros Documentos</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>parecer_final.pdf</t>
+          <t>errata_-_modelo_de_proposta.pdf</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/6b/a4/6ba43270-aa75-42ff-8566-e3cb6fa2854b/parecer_final.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/ff/c8/ffc87811-1479-48fb-865a-3a2ad7cf0ceb/errata_-_modelo_de_proposta.pdf</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -7611,7 +7611,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 76/2024 - Serviço de Limpeza SESILAb — Esclarecimento nº 1</t>
+          <t>Chamamento Público nº 76/2024 - Serviço de Limpeza SESILAb — Aviso de Cancelamento</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -7647,12 +7647,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>esclarecimento_1.pdf</t>
+          <t>aviso_de_cancelamento_-.pdf</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/39/72/3972186b-a205-46c2-a044-30b5c0adacf5/esclarecimento_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/3d/21/3d21d7e1-0eaa-4e87-a53f-a6217b4a5046/aviso_de_cancelamento_-.pdf</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -7666,7 +7666,7 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7686,13 +7686,13 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 76/2024 - Serviço de Limpeza SESILAb — Aviso de Suspensão</t>
+          <t>CHAMAMENTO PÚBLICO-87-2024-Locação de equipamentos — Relatório de Julgamento/cancelamento.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-01-09 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2024-12-20 | Outros Documentos</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>aviso_de_suspensao.pdf</t>
+          <t>julgamento_de_reconsideracao_-_locacao_de_equipamentos_de_ti_-_robotica.pdf</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/58/17/5817da8e-db21-4a84-8c84-36b8ff2f4b7a/aviso_de_suspensao.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/76/6f/766fff72-cc09-4224-bd08-22c29a10af7e/julgamento_de_reconsideracao_-_locacao_de_equipamentos_de_ti_-_robotica.pdf</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -7721,7 +7721,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7741,13 +7741,13 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 76/2024 - Serviço de Limpeza SESILAb — Comunicado de Recesso 2024-2025</t>
+          <t>CHAMAMENTO PUBLICO-79-2024 - Capacitação Multiplicadores FTC e FIRST — Parecer Final</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-01-09 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-12-09 | Outros Documentos</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>comunicado_recesso_2024-2025.pdf</t>
+          <t>parecer_final.pdf</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/86/4c/864c9059-d302-4dc8-a0b3-14ac10431b10/comunicado_recesso_2024-2025.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/8b/a6/8ba6d16c-7f03-4c09-b6b3-2e7a43a9b774/parecer_final.pdf</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -7776,7 +7776,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7796,13 +7796,13 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 76/2024 - Serviço de Limpeza SESILAb — Errata - Modelo de Proposta</t>
+          <t>Chamamento Público 75/2024 - Serviço de Vigilância, Brigadista e Port — Esclarecimento 1</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-01-09 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2024-12-02 | Outros Documentos</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>errata_-_modelo_de_proposta.pdf</t>
+          <t>esclarecimento_1.pdf</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/ff/c8/ffc87811-1479-48fb-865a-3a2ad7cf0ceb/errata_-_modelo_de_proposta.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/23/1e/231e8285-4665-4597-be56-1194628c4216/esclarecimento_1.pdf</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -7831,7 +7831,7 @@
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7851,13 +7851,13 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 76/2024 - Serviço de Limpeza SESILAb — Aviso de Cancelamento</t>
+          <t>Chamamento Público nº 74/2024 - Contratação de CFTV para SESI LAB — Aviso de Cancelamento</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2025-01-09 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2024-11-27 | Outros Documentos</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>aviso_de_cancelamento_-.pdf</t>
+          <t>aviso_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/3d/21/3d21d7e1-0eaa-4e87-a53f-a6217b4a5046/aviso_de_cancelamento_-.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/99/e3/99e3ff50-a671-469e-9322-a8c0268443f4/aviso_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -7886,7 +7886,7 @@
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7906,13 +7906,13 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PÚBLICO-87-2024-Locação de equipamentos — Relatório de Julgamento/cancelamento.</t>
+          <t>Chamamento Público nº 69/2024 - Posicionamento de Marketing — Despacho de Cancelamento</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2024-12-20 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2024-11-19 | Outros Documentos</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -7922,12 +7922,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>julgamento_de_reconsideracao_-_locacao_de_equipamentos_de_ti_-_robotica.pdf</t>
+          <t>despacho_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/76/6f/766fff72-cc09-4224-bd08-22c29a10af7e/julgamento_de_reconsideracao_-_locacao_de_equipamentos_de_ti_-_robotica.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/73/b5/73b568bf-6475-4883-b501-8a057b13beff/despacho_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -7941,7 +7941,7 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -7961,13 +7961,13 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO-79-2024 - Capacitação Multiplicadores FTC e FIRST — Parecer Final</t>
+          <t>Chamamento Público nº 57/2024 - Manutenção de Paisagismo SESILab — Aviso de Adiamento CP 57-2024</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-12-09 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-10-23 | Outros Documentos</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>parecer_final.pdf</t>
+          <t>aviso_de_adiamento_-_cp_57-2024.pdf</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/8b/a6/8ba6d16c-7f03-4c09-b6b3-2e7a43a9b774/parecer_final.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/85/fd/85fdbf46-7661-40fe-a01c-14d8b60c0b3f/aviso_de_adiamento_-_cp_57-2024.pdf</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -7996,7 +7996,7 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8016,13 +8016,13 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Chamamento Público 75/2024 - Serviço de Vigilância, Brigadista e Port — Esclarecimento 1</t>
+          <t>Chamamento Público nº 57/2024 - Manutenção de Paisagismo SESILab — Aviso de Adiamento CP 57-2024</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2024-12-02 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-10-23 | Outros Documentos</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>esclarecimento_1.pdf</t>
+          <t>aviso_de_adiamento_-_cp_57-2024_-_01-11-2024.pdf</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/23/1e/231e8285-4665-4597-be56-1194628c4216/esclarecimento_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/05/9b/059bddfc-2114-49b5-b9b3-adacc67c0b81/aviso_de_adiamento_-_cp_57-2024_-_01-11-2024.pdf</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -8051,7 +8051,7 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8071,13 +8071,13 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 74/2024 - Contratação de CFTV para SESI LAB — Aviso de Cancelamento</t>
+          <t>Chamamento Público nº 56/2024 - SEMINÁRIO SAÚDE NA INDUSTRIA - GLOBAL — PARECER FINAL</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2024-11-27 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-10-18 | Outros Documentos</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>aviso_de_cancelamento.pdf</t>
+          <t>parecer_final.pdf</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/99/e3/99e3ff50-a671-469e-9322-a8c0268443f4/aviso_de_cancelamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/c4/b9/c4b91e66-f8b3-4edf-8fa1-f463b32527b9/parecer_final.pdf</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -8106,7 +8106,7 @@
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8126,13 +8126,13 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 69/2024 - Posicionamento de Marketing — Despacho de Cancelamento</t>
+          <t>Chamamento Público CP 47/2024 - Análise de Dados — Resposta ao pedido de esclarecimento</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2024-11-19 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-10-03 | Outros Documentos</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>despacho_de_cancelamento.pdf</t>
+          <t>esclarecimento_1_respostas.pdf</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/73/b5/73b568bf-6475-4883-b501-8a057b13beff/despacho_de_cancelamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/cf/39/cf39b418-5ce7-449e-b39a-621e1dc38377/esclarecimento_1_respostas.pdf</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -8161,7 +8161,7 @@
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8181,13 +8181,13 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 57/2024 - Manutenção de Paisagismo SESILab — Aviso de Adiamento CP 57-2024</t>
+          <t>Chamamento Público CP 47/2024 - Análise de Dados — PARECER FINAL</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-10-23 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-10-03</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>aviso_de_adiamento_-_cp_57-2024.pdf</t>
+          <t>parecer_final.pdf</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/85/fd/85fdbf46-7661-40fe-a01c-14d8b60c0b3f/aviso_de_adiamento_-_cp_57-2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f6/9b/f69bee24-aab8-4bd3-a5af-a15452b1906f/parecer_final.pdf</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -8216,7 +8216,7 @@
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8236,13 +8236,13 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 57/2024 - Manutenção de Paisagismo SESILab — Aviso de Adiamento CP 57-2024</t>
+          <t>CHAMAMENTO PÚBLICO 46-2024 - RP MOBILIÁRIO ESCOLAR SESI — Julgamento impugnação</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-10-23 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2024-10-02 | Outros Documentos</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>aviso_de_adiamento_-_cp_57-2024_-_01-11-2024.pdf</t>
+          <t>cp_46-2024__julgamento.pdf</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/05/9b/059bddfc-2114-49b5-b9b3-adacc67c0b81/aviso_de_adiamento_-_cp_57-2024_-_01-11-2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/52/fa/52fa19f8-3aa5-4b14-a973-a8623217c06e/cp_46-2024__julgamento.pdf</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -8271,7 +8271,7 @@
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8291,13 +8291,13 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Chamamento Público nº 56/2024 - SEMINÁRIO SAÚDE NA INDUSTRIA - GLOBAL — PARECER FINAL</t>
+          <t>CHAMAMENTO PÚBLICO 46-2024 - RP MOBILIÁRIO ESCOLAR SESI — Resposta Esclarecimento</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-10-18 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2024-10-02 | Outros Documentos</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>parecer_final.pdf</t>
+          <t>resposta_cp_46-2024__julgamen_1.pdf</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/c4/b9/c4b91e66-f8b3-4edf-8fa1-f463b32527b9/parecer_final.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/05/6e/056e0e86-55f0-4823-8190-efaef1a4dcf2/resposta_cp_46-2024__julgamen_1.pdf</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -8326,7 +8326,7 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8346,13 +8346,13 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Chamamento Público CP 47/2024 - Análise de Dados — Resposta ao pedido de esclarecimento</t>
+          <t>Chamamento Público CP 3/2024 - Produção de Audiovisuais — AVISO DE RECESSO</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-10-03 | Outros Documentos</t>
+          <t>Processos de contratação | CNI, SESI, SENAI | RCA Disputa Fechada | Em andamento | Abertura: 2024-09-30 | Outros Documentos</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>esclarecimento_1_respostas.pdf</t>
+          <t>aviso_de_recesso.pdf</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/cf/39/cf39b418-5ce7-449e-b39a-621e1dc38377/esclarecimento_1_respostas.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/2c/d1/2cd1e5ca-2669-4fbe-81f2-d76a287cf9f7/aviso_de_recesso.pdf</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -8381,7 +8381,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8401,13 +8401,13 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Chamamento Público CP 47/2024 - Análise de Dados — PARECER FINAL</t>
+          <t>Chamamento Público CP 38/2024 - Curso Online FLL — Empresas Participantes</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-10-03</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-09-23 | Participantes</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>parecer_final.pdf</t>
+          <t>empresas_participantes_38-24.pdf</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f6/9b/f69bee24-aab8-4bd3-a5af-a15452b1906f/parecer_final.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/00/85/00851685-bd11-45e9-abca-255f85c67732/empresas_participantes_38-24.pdf</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -8436,7 +8436,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8456,13 +8456,13 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PÚBLICO 46-2024 - RP MOBILIÁRIO ESCOLAR SESI — Julgamento impugnação</t>
+          <t>Chamamento Público CP 38/2024 - Curso Online FLL — 01/10/2024</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2024-10-02 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-09-23 | Data: RLC - Homologação / RCA - Resultado Final</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>cp_46-2024__julgamento.pdf</t>
+          <t>parecer_final.pdf</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/52/fa/52fa19f8-3aa5-4b14-a973-a8623217c06e/cp_46-2024__julgamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/8e/9a/8e9aa1b8-11af-4881-a4ef-62c6eab6be2c/parecer_final.pdf</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -8491,7 +8491,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8511,13 +8511,13 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PÚBLICO 46-2024 - RP MOBILIÁRIO ESCOLAR SESI — Resposta Esclarecimento</t>
+          <t>CHAMAMENTO PÚBLICO-34-2024-Marketing e posicionamento de produto. — Aviso de Cancelamento</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Em andamento | Abertura: 2024-10-02 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2024-09-04 | Outros Documentos</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>resposta_cp_46-2024__julgamen_1.pdf</t>
+          <t>aviso_de_cancelamento_assinado.pdf</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/05/6e/056e0e86-55f0-4823-8190-efaef1a4dcf2/resposta_cp_46-2024__julgamen_1.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/fc/10/fc10be05-4cd9-4603-b686-7013591b53f8/aviso_de_cancelamento_assinado.pdf</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -8546,7 +8546,7 @@
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8566,13 +8566,13 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Chamamento Público CP 3/2024 - Produção de Audiovisuais — AVISO DE RECESSO</t>
+          <t>Chamamento Público CP 27/2024 - Bilheteria Digital — Condições Gerais da Contratação</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Processos de contratação | CNI, SESI, SENAI | RCA Disputa Fechada | Em andamento | Abertura: 2024-09-30 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2024-08-29 | Edital/Chamamento</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>aviso_de_recesso.pdf</t>
+          <t>contrato_de_prestacao_de_servicos__condicoes_gerais__rca.pdf</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/2c/d1/2cd1e5ca-2669-4fbe-81f2-d76a287cf9f7/aviso_de_recesso.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/2e/c5/2ec53885-1095-43f9-a45b-f152132535e6/contrato_de_prestacao_de_servicos__condicoes_gerais__rca.pdf</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -8601,7 +8601,7 @@
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8621,13 +8621,13 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Chamamento Público CP 38/2024 - Curso Online FLL — Empresas Participantes</t>
+          <t>CHAMAMENTO PUBLICO-4-2024 - UTI móvel — Participantes 4/2024</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-09-23 | Participantes</t>
+          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-05-24 | Participantes</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>empresas_participantes_38-24.pdf</t>
+          <t>relatorio_de_lances_-_participantes.pdf</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/00/85/00851685-bd11-45e9-abca-255f85c67732/empresas_participantes_38-24.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/5a/fb/5afb1297-6049-4c8c-aa56-d21379cbaed3/relatorio_de_lances_-_participantes.pdf</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -8656,7 +8656,7 @@
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8676,13 +8676,13 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Chamamento Público CP 38/2024 - Curso Online FLL — 01/10/2024</t>
+          <t>Edital PE 32/2024 - Fornecimento de notebooks — Recurso Positovo Lote 2</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-09-23 | Data: RLC - Homologação / RCA - Resultado Final</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Em andamento | Abertura: 2024-04-18 | Outros Documentos</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>parecer_final.pdf</t>
+          <t>recurso_positivo.pdf</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/8e/9a/8e9aa1b8-11af-4881-a4ef-62c6eab6be2c/parecer_final.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/2c/b0/2cb0833c-880f-4c73-955e-7375a681a194/recurso_positivo.pdf</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -8711,7 +8711,7 @@
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8731,13 +8731,13 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PÚBLICO-34-2024-Marketing e posicionamento de produto. — Aviso de Cancelamento</t>
+          <t>PE 13 /2024 - Locação de equipamentos de transmissão, streaming — Participantes PE-13/2024</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2024-09-04 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2024-02-16 | Participantes</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>aviso_de_cancelamento_assinado.pdf</t>
+          <t>participantes_pe-13-2024.pdf</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/fc/10/fc10be05-4cd9-4603-b686-7013591b53f8/aviso_de_cancelamento_assinado.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/7e/9c/7e9c3750-5134-4970-82e1-20ff7a4e93bd/participantes_pe-13-2024.pdf</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -8766,7 +8766,7 @@
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8786,13 +8786,13 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Chamamento Público CP 27/2024 - Bilheteria Digital — Condições Gerais da Contratação</t>
+          <t>PE 4/2024 - AQUISIÇÃO DE NOTEBOOKS — Resposta 16 do Esclarecimento 4</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Cancelado | Abertura: 2024-08-29 | Edital/Chamamento</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2024-01-23 | Outros Documentos</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>contrato_de_prestacao_de_servicos__condicoes_gerais__rca.pdf</t>
+          <t>resposta_16_-_carta_-_shape_the_future_da_microsoft.pdf</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/2e/c5/2ec53885-1095-43f9-a45b-f152132535e6/contrato_de_prestacao_de_servicos__condicoes_gerais__rca.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/09/d2/09d2c72a-5dcb-4b11-9eb7-b7b696b7b4eb/resposta_16_-_carta_-_shape_the_future_da_microsoft.pdf</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -8821,7 +8821,7 @@
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8841,13 +8841,13 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>CHAMAMENTO PUBLICO-4-2024 - UTI móvel — Participantes 4/2024</t>
+          <t>PE 4/2024 - AQUISIÇÃO DE NOTEBOOKS — Cancelamento</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RCA Disputa Aberta | Encerrado/Concluído | Abertura: 2024-05-24 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2024-01-23 | Outros Documentos</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>relatorio_de_lances_-_participantes.pdf</t>
+          <t>dou-pe_04-2024_cancelamento_publicado_em_270324.pdf</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/5a/fb/5afb1297-6049-4c8c-aa56-d21379cbaed3/relatorio_de_lances_-_participantes.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/d6/59/d6597e72-31ea-4f71-9730-2b36d876348a/dou-pe_04-2024_cancelamento_publicado_em_270324.pdf</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -8876,7 +8876,7 @@
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8896,13 +8896,13 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Edital PE 32/2024 - Fornecimento de notebooks — Recurso Positovo Lote 2</t>
+          <t>PE 100/2023 - Serviço de vigilância Festival de Robótica — Empresas Participantes</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Em andamento | Abertura: 2024-04-18 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-12-20 | Participantes</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>recurso_positivo.pdf</t>
+          <t>participantes_-_relatoriomapacomparativoprecos_13.pdf</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/2c/b0/2cb0833c-880f-4c73-955e-7375a681a194/recurso_positivo.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/04/1a/041a63dc-45ff-4248-905b-86c105340745/participantes_-_relatoriomapacomparativoprecos_13.pdf</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -8931,7 +8931,7 @@
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -8951,13 +8951,13 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>PE 13 /2024 - Locação de equipamentos de transmissão, streaming — Participantes PE-13/2024</t>
+          <t>PP 77/2023 - Aquisição de Notebooks — Aviso de Cancelamento</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2024-02-16 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-11-09 | Outros Documentos</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>participantes_pe-13-2024.pdf</t>
+          <t>aviso_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/7e/9c/7e9c3750-5134-4970-82e1-20ff7a4e93bd/participantes_pe-13-2024.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/93/e9/93e922e7-ae6c-4d8c-88f0-270a22a6582a/aviso_de_cancelamento.pdf</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -8986,7 +8986,7 @@
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9006,13 +9006,13 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>PE 4/2024 - AQUISIÇÃO DE NOTEBOOKS — Resposta 16 do Esclarecimento 4</t>
+          <t>PP 77/2023 - Aquisição de Notebooks — Extrato do Aviso de Cancelamento (DOU)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2024-01-23 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-11-09 | Outros Documentos</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>resposta_16_-_carta_-_shape_the_future_da_microsoft.pdf</t>
+          <t>dou_pe-77-2023_aviso_de_cancelamento_publicado_em_16112023.pdf</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/09/d2/09d2c72a-5dcb-4b11-9eb7-b7b696b7b4eb/resposta_16_-_carta_-_shape_the_future_da_microsoft.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/d2/0a/d20af794-3439-4382-a1de-14aa568800e3/dou_pe-77-2023_aviso_de_cancelamento_publicado_em_16112023.pdf</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -9041,7 +9041,7 @@
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9061,13 +9061,13 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>PE 4/2024 - AQUISIÇÃO DE NOTEBOOKS — Cancelamento</t>
+          <t>PP 78/2023 - Montagem festival de Robótica — Anexo IA - Cadernos de Especificação Técnica</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2024-01-23 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-10-24 | Edital/Chamamento</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9077,12 +9077,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>dou-pe_04-2024_cancelamento_publicado_em_270324.pdf</t>
+          <t>anexo_ia_-_caderno_tecnico-festivalsesiderobotica-2024-v01.pdf</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/d6/59/d6597e72-31ea-4f71-9730-2b36d876348a/dou-pe_04-2024_cancelamento_publicado_em_270324.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/74/da/74da557f-7e7c-4698-86eb-1113e2ffd8de/anexo_ia_-_caderno_tecnico-festivalsesiderobotica-2024-v01.pdf</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -9093,10 +9093,12 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
+      <c r="L157" t="n">
+        <v>42655.72</v>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9116,13 +9118,13 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>PE 100/2023 - Serviço de vigilância Festival de Robótica — Empresas Participantes</t>
+          <t>PP 78/2023 - Montagem festival de Robótica — Anexo IB - Cadernos de Especificação Técnica</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-12-20 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-10-24 | Edital/Chamamento</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9132,12 +9134,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>participantes_-_relatoriomapacomparativoprecos_13.pdf</t>
+          <t>anexo_ib_-festival_internacional_sesi_de_robotica_-_projeto.pdf</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/04/1a/041a63dc-45ff-4248-905b-86c105340745/participantes_-_relatoriomapacomparativoprecos_13.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/8e/36/8e369f35-1aa2-4726-ac3b-a13198bf7c75/anexo_ib_-festival_internacional_sesi_de_robotica_-_projeto.pdf</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -9148,10 +9150,12 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr"/>
+      <c r="L158" t="n">
+        <v>46294.89</v>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9171,13 +9175,13 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PP 77/2023 - Aquisição de Notebooks — Aviso de Cancelamento</t>
+          <t>PP 78/2023 - Montagem festival de Robótica — Anexo II A - Cadernos de Especificação Técnica</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-11-09 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-10-24 | Edital/Chamamento</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9187,12 +9191,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>aviso_de_cancelamento.pdf</t>
+          <t>anexo_iia-caderno_tecnico-openrobotics2024-v01_2.pdf</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/93/e9/93e922e7-ae6c-4d8c-88f0-270a22a6582a/aviso_de_cancelamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/5c/57/5c57afe3-424d-43fe-ad51-ebefa15e1e4a/anexo_iia-caderno_tecnico-openrobotics2024-v01_2.pdf</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -9203,10 +9207,12 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr"/>
+      <c r="L159" t="n">
+        <v>63724.28</v>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9226,13 +9232,13 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PP 77/2023 - Aquisição de Notebooks — Extrato do Aviso de Cancelamento (DOU)</t>
+          <t>PP 78/2023 - Montagem festival de Robótica — Anexo IIB - Cadernos de Especificação Técnica</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-11-09 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-10-24 | Edital/Chamamento</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9242,12 +9248,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>dou_pe-77-2023_aviso_de_cancelamento_publicado_em_16112023.pdf</t>
+          <t>anexo_iib_-_festival_sesi_de_robotica_2024-_projeto_bsb.pdf</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/d2/0a/d20af794-3439-4382-a1de-14aa568800e3/dou_pe-77-2023_aviso_de_cancelamento_publicado_em_16112023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f7/96/f796d9b6-9359-428b-b455-04ad939c01ed/anexo_iib_-_festival_sesi_de_robotica_2024-_projeto_bsb.pdf</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -9258,10 +9264,12 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
+      <c r="L160" t="n">
+        <v>20815.56</v>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9281,13 +9289,13 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>PP 78/2023 - Montagem festival de Robótica — Anexo IA - Cadernos de Especificação Técnica</t>
+          <t>Edital Credenciamento 2/2023 -  Produção de estudos, dashboards</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-10-24 | Edital/Chamamento</t>
+          <t>Processos de contratação | SESI, SENAI | RLC Credenciamento | Em andamento | Abertura: 2023-10-03 | Edital/Chamamento</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9297,12 +9305,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>anexo_ia_-_caderno_tecnico-festivalsesiderobotica-2024-v01.pdf</t>
+          <t>chamada_de_credenciamento_2-2023.pdf</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/74/da/74da557f-7e7c-4698-86eb-1113e2ffd8de/anexo_ia_-_caderno_tecnico-festivalsesiderobotica-2024-v01.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/37/57/3757b967-b4a8-4f83-adda-7ff5200169b0/chamada_de_credenciamento_2-2023.pdf</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -9313,12 +9321,10 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L161" t="n">
-        <v>42655.72</v>
-      </c>
+      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9338,13 +9344,13 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>PP 78/2023 - Montagem festival de Robótica — Anexo IB - Cadernos de Especificação Técnica</t>
+          <t>PP 73/2023 - Solução “Aprendizagem Integrada de Língua Inglesa” — CANCELAMENTO</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-10-24 | Edital/Chamamento</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-09-14 | Outros Documentos</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9354,12 +9360,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>anexo_ib_-festival_internacional_sesi_de_robotica_-_projeto.pdf</t>
+          <t>dou_pp-732023_-_cancelamento_-__publicado_em_18122023.pdf</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/8e/36/8e369f35-1aa2-4726-ac3b-a13198bf7c75/anexo_ib_-festival_internacional_sesi_de_robotica_-_projeto.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f8/7c/f87cbced-b982-42e2-a056-46f935ea15c7/dou_pp-732023_-_cancelamento_-__publicado_em_18122023.pdf</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -9370,12 +9376,10 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L162" t="n">
-        <v>46294.89</v>
-      </c>
+      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9395,13 +9399,13 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>PP 78/2023 - Montagem festival de Robótica — Anexo II A - Cadernos de Especificação Técnica</t>
+          <t>Edital PE 72/2023 -  Serviços de Impressão — Aviso de Adiamento</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-10-24 | Edital/Chamamento</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-09-13 | Outros Documentos</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -9411,12 +9415,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>anexo_iia-caderno_tecnico-openrobotics2024-v01_2.pdf</t>
+          <t>dou_pe_72-2023_-_aviso_de_adiamento_publicado_em_13092023.pdf</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/5c/57/5c57afe3-424d-43fe-ad51-ebefa15e1e4a/anexo_iia-caderno_tecnico-openrobotics2024-v01_2.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/23/c7/23c76b81-e9ea-451a-9342-da188cd2550d/dou_pe_72-2023_-_aviso_de_adiamento_publicado_em_13092023.pdf</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -9427,12 +9431,10 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L163" t="n">
-        <v>63724.28</v>
-      </c>
+      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9452,13 +9454,13 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>PP 78/2023 - Montagem festival de Robótica — Anexo IIB - Cadernos de Especificação Técnica</t>
+          <t>Edital PE 45/2023 -  Lego Robótica FLL 2023-2024 — Publicação do certame</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-10-24 | Edital/Chamamento</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-07-26 | Outros Documentos</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -9468,12 +9470,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>anexo_iib_-_festival_sesi_de_robotica_2024-_projeto_bsb.pdf</t>
+          <t>dou_pe-452023_publicado_em_14072023.pdf</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f7/96/f796d9b6-9359-428b-b455-04ad939c01ed/anexo_iib_-_festival_sesi_de_robotica_2024-_projeto_bsb.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/53/dd/53dd8ed7-25e3-4ed1-90b5-027adbb2d928/dou_pe-452023_publicado_em_14072023.pdf</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -9484,12 +9486,10 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L164" t="n">
-        <v>20815.56</v>
-      </c>
+      <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9509,13 +9509,13 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Edital Credenciamento 2/2023 -  Produção de estudos, dashboards</t>
+          <t>PE 51-2023 - Transporte visitas escolares SESI LAB — Republicação</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI, SENAI | RLC Credenciamento | Em andamento | Abertura: 2023-10-03 | Edital/Chamamento</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-07-12 | Outros Documentos</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>chamada_de_credenciamento_2-2023.pdf</t>
+          <t>dou_pe_512023_-_republicacao_publicado_em_13072023.pdf</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/37/57/3757b967-b4a8-4f83-adda-7ff5200169b0/chamada_de_credenciamento_2-2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/42/cc/42cc9f16-63a7-4515-a8da-908e99867be0/dou_pe_512023_-_republicacao_publicado_em_13072023.pdf</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -9544,7 +9544,7 @@
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9564,13 +9564,13 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>PP 73/2023 - Solução “Aprendizagem Integrada de Língua Inglesa” — CANCELAMENTO</t>
+          <t>PE 51-2023 - Transporte visitas escolares SESI LAB — Republicação</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-09-14 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-07-12 | Outros Documentos</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9580,12 +9580,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>dou_pp-732023_-_cancelamento_-__publicado_em_18122023.pdf</t>
+          <t>dou_pe_512023_-_republicacao2_publicado_em_21072023.pdf</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f8/7c/f87cbced-b982-42e2-a056-46f935ea15c7/dou_pp-732023_-_cancelamento_-__publicado_em_18122023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/9e/dd/9edd03d8-8ed8-4f00-ac28-12dc5d582915/dou_pe_512023_-_republicacao2_publicado_em_21072023.pdf</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -9599,7 +9599,7 @@
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9619,13 +9619,13 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Edital PE 72/2023 -  Serviços de Impressão — Aviso de Adiamento</t>
+          <t>PE 51-2023 - Transporte visitas escolares SESI LAB — CANCELAMENTO</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-09-13 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-07-12 | Outros Documentos</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>dou_pe_72-2023_-_aviso_de_adiamento_publicado_em_13092023.pdf</t>
+          <t>dou_pe_512023_-_cancelamento_publicado_em_08082023.pdf</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/23/c7/23c76b81-e9ea-451a-9342-da188cd2550d/dou_pe_72-2023_-_aviso_de_adiamento_publicado_em_13092023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/96/11/9611b995-2103-4c9c-82fa-7b4b7a5ba816/dou_pe_512023_-_cancelamento_publicado_em_08082023.pdf</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -9654,7 +9654,7 @@
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9674,13 +9674,13 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Edital PE 45/2023 -  Lego Robótica FLL 2023-2024 — Publicação do certame</t>
+          <t>PE 47/2023 - Switch de Rede — Participantes PE 47/2023</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-07-26 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-07-03 | Participantes</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>dou_pe-452023_publicado_em_14072023.pdf</t>
+          <t>participantes_pe_47-2023.pdf</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/53/dd/53dd8ed7-25e3-4ed1-90b5-027adbb2d928/dou_pe-452023_publicado_em_14072023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/57/6e/576ee24f-37a2-4141-9e28-f215c3c23a0b/participantes_pe_47-2023.pdf</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -9709,7 +9709,7 @@
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9729,13 +9729,13 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>PE 51-2023 - Transporte visitas escolares SESI LAB — Republicação</t>
+          <t>PE 44/2023 - Aquisição de Access Points — Participantes PE-4/2023</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-07-12 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-06-19 | Participantes</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>dou_pe_512023_-_republicacao_publicado_em_13072023.pdf</t>
+          <t>participantes_pe_44-2023.pdf</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/42/cc/42cc9f16-63a7-4515-a8da-908e99867be0/dou_pe_512023_-_republicacao_publicado_em_13072023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/3d/8b/3d8b1a7c-2877-423a-bbf5-ca8996b59df4/participantes_pe_44-2023.pdf</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -9764,7 +9764,7 @@
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9784,13 +9784,13 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>PE 51-2023 - Transporte visitas escolares SESI LAB — Republicação</t>
+          <t>PP 18/203 - Montagem Festival Internacional Robótica — Anexo IA</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-07-12 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-05-24 | Outros Documentos</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>dou_pe_512023_-_republicacao2_publicado_em_21072023.pdf</t>
+          <t>anexo_ia_-_caderno_tecnico_-_festival_internacional_sesi_de_robotica_2023_v01b_compressed.pdf</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/9e/dd/9edd03d8-8ed8-4f00-ac28-12dc5d582915/dou_pe_512023_-_republicacao2_publicado_em_21072023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/bf/f7/bff75cf6-52e3-43a0-b6be-961adbcc3bfb/anexo_ia_-_caderno_tecnico_-_festival_internacional_sesi_de_robotica_2023_v01b_compressed.pdf</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -9816,10 +9816,12 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr"/>
+      <c r="L170" t="n">
+        <v>64522.37</v>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9839,13 +9841,13 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>PE 51-2023 - Transporte visitas escolares SESI LAB — CANCELAMENTO</t>
+          <t>PE 29/2023 - ORIENTADORES DE PÚBLICO — Participantes PE 29/2023</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-07-12 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-05-03 | Participantes</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -9855,12 +9857,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>dou_pe_512023_-_cancelamento_publicado_em_08082023.pdf</t>
+          <t>participantes_pe-29-2023.pdf</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/96/11/9611b995-2103-4c9c-82fa-7b4b7a5ba816/dou_pe_512023_-_cancelamento_publicado_em_08082023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/61/1c/611c5409-6d20-4393-a10d-755ef1400f49/participantes_pe-29-2023.pdf</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -9874,7 +9876,7 @@
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9894,13 +9896,13 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>PE 47/2023 - Switch de Rede — Participantes PE 47/2023</t>
+          <t>Edital Credenciamento 1/2023 -  Produção de estudos, dashboards</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-07-03 | Participantes</t>
+          <t>Processos de contratação | SESI, SENAI | RLC Credenciamento | Encerrado/Concluído | Abertura: 2023-03-23 | Edital/Chamamento</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -9910,12 +9912,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>participantes_pe_47-2023.pdf</t>
+          <t>chamamento_publico_01-_2023_credenciamento_servicos_tecnicos.pdf</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/57/6e/576ee24f-37a2-4141-9e28-f215c3c23a0b/participantes_pe_47-2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/73/07/7307afb8-ec70-4c78-b207-2d2fe1081674/chamamento_publico_01-_2023_credenciamento_servicos_tecnicos.pdf</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -9929,7 +9931,7 @@
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -9949,13 +9951,13 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>PE 44/2023 - Aquisição de Access Points — Participantes PE-4/2023</t>
+          <t>Edital Credenciamento 1/2023 -  Produção de estudos, dashboards — ERRATA 1</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-06-19 | Participantes</t>
+          <t>Processos de contratação | SESI, SENAI | RLC Credenciamento | Encerrado/Concluído | Abertura: 2023-03-23 | Outros Documentos</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -9965,12 +9967,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>participantes_pe_44-2023.pdf</t>
+          <t>errata1_credenciamento.pdf</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/3d/8b/3d8b1a7c-2877-423a-bbf5-ca8996b59df4/participantes_pe_44-2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/5d/1a/5d1a503a-1281-4d43-8165-4de9c0d734ca/errata1_credenciamento.pdf</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -9984,7 +9986,7 @@
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10004,13 +10006,13 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>PP 18/203 - Montagem Festival Internacional Robótica — Anexo IA</t>
+          <t>PP 24/2023 - Aquisição de Simuladores na área de Ciências — Publicação do certame</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-05-24 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-03-22 | Outros Documentos</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10020,12 +10022,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>anexo_ia_-_caderno_tecnico_-_festival_internacional_sesi_de_robotica_2023_v01b_compressed.pdf</t>
+          <t>dou_-_pp_24-2023_publicado_em_13032023.pdf</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/bf/f7/bff75cf6-52e3-43a0-b6be-961adbcc3bfb/anexo_ia_-_caderno_tecnico_-_festival_internacional_sesi_de_robotica_2023_v01b_compressed.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/e6/43/e6436adf-af5c-4e1c-94e0-7d142a595382/dou_-_pp_24-2023_publicado_em_13032023.pdf</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -10036,12 +10038,10 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="L174" t="n">
-        <v>64522.37</v>
-      </c>
+      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10061,13 +10061,13 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>PE 29/2023 - ORIENTADORES DE PÚBLICO — Participantes PE 29/2023</t>
+          <t>PP 24/2023 - Aquisição de Simuladores na área de Ciências — Publicação_DOU_adiamento</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-05-03 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-03-22 | Outros Documentos</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>participantes_pe-29-2023.pdf</t>
+          <t>dou_-_pp_24-2023_adiamento_publicado_em_17032023.pdf</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/61/1c/611c5409-6d20-4393-a10d-755ef1400f49/participantes_pe-29-2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/34/df/34df82ec-1c83-45f0-93d4-e5beb547c6f1/dou_-_pp_24-2023_adiamento_publicado_em_17032023.pdf</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -10096,7 +10096,7 @@
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10116,13 +10116,13 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Edital Credenciamento 1/2023 -  Produção de estudos, dashboards</t>
+          <t>CR 25/2023 - Reforma e Modernização - Espaço SESI Inovação — Anexo_Esclarecimento 01_Planilha_valores_referência</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI, SENAI | RLC Credenciamento | Encerrado/Concluído | Abertura: 2023-03-23 | Edital/Chamamento</t>
+          <t>Processos de contratação | SESI | RLC Concorrência | Encerrado/Concluído | Abertura: 2023-03-03 | Outros Documentos</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>chamamento_publico_01-_2023_credenciamento_servicos_tecnicos.pdf</t>
+          <t>planilha_de_valores_referencia.pdf</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/73/07/7307afb8-ec70-4c78-b207-2d2fe1081674/chamamento_publico_01-_2023_credenciamento_servicos_tecnicos.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/48/26/48266b62-7286-4a47-87c0-cbc06ac03a94/planilha_de_valores_referencia.pdf</t>
         </is>
       </c>
       <c r="J176" t="n">
@@ -10151,7 +10151,7 @@
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10171,13 +10171,13 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Edital Credenciamento 1/2023 -  Produção de estudos, dashboards — ERRATA 1</t>
+          <t>CR 25/2023 - Reforma e Modernização - Espaço SESI Inovação — Material Técnico Stripscreen</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI, SENAI | RLC Credenciamento | Encerrado/Concluído | Abertura: 2023-03-23 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Concorrência | Encerrado/Concluído | Abertura: 2023-03-03 | Outros Documentos</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>errata1_credenciamento.pdf</t>
+          <t>manual_tecnico_stripscreen.pdf</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/5d/1a/5d1a503a-1281-4d43-8165-4de9c0d734ca/errata1_credenciamento.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/95/04/95042680-31f4-468a-964f-c57c5793c943/manual_tecnico_stripscreen.pdf</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -10206,7 +10206,7 @@
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10226,13 +10226,13 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>PP 24/2023 - Aquisição de Simuladores na área de Ciências — Publicação do certame</t>
+          <t>CR 25/2023 - Reforma e Modernização - Espaço SESI Inovação — Planilha referencia de orçamento com valores - BDI Diferenciado</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-03-22 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Concorrência | Encerrado/Concluído | Abertura: 2023-03-03 | Outros Documentos</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>dou_-_pp_24-2023_publicado_em_13032023.pdf</t>
+          <t>planilha_referencia_de_orcamento_com_valores_-_bdi_diferenciado.pdf</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/e6/43/e6436adf-af5c-4e1c-94e0-7d142a595382/dou_-_pp_24-2023_publicado_em_13032023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/0a/78/0a7888b7-5aff-49d9-95bb-6dbb59923df9/planilha_referencia_de_orcamento_com_valores_-_bdi_diferenciado.pdf</t>
         </is>
       </c>
       <c r="J178" t="n">
@@ -10261,7 +10261,7 @@
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10281,13 +10281,13 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>PP 24/2023 - Aquisição de Simuladores na área de Ciências — Publicação_DOU_adiamento</t>
+          <t>PE 06/2023 - Plataforma sistema SESI de educação Adaptativo Digital — Anexo III Contrato - Condições Gerais</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2023-03-22 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-27 | Edital/Chamamento</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -10297,12 +10297,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>dou_-_pp_24-2023_adiamento_publicado_em_17032023.pdf</t>
+          <t>contrato_de_prestacao_de_servicos_-_condicoes_gerais_cnisesisenaiiel.pdf</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/34/df/34df82ec-1c83-45f0-93d4-e5beb547c6f1/dou_-_pp_24-2023_adiamento_publicado_em_17032023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/1a/2a/1a2a0f5c-1a77-489f-85d3-befedfd2ed20/contrato_de_prestacao_de_servicos_-_condicoes_gerais_cnisesisenaiiel.pdf</t>
         </is>
       </c>
       <c r="J179" t="n">
@@ -10316,7 +10316,7 @@
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10336,13 +10336,13 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>CR 25/2023 - Reforma e Modernização - Espaço SESI Inovação — Anexo_Esclarecimento 01_Planilha_valores_referência</t>
+          <t>PE 06/2023 - Plataforma sistema SESI de educação Adaptativo Digital — Aviso de Adiamento</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Concorrência | Encerrado/Concluído | Abertura: 2023-03-03 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-27 | Outros Documentos</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>planilha_de_valores_referencia.pdf</t>
+          <t>dou_pe_6-2023_adiamento_publicado_em_24022023.pdf</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/48/26/48266b62-7286-4a47-87c0-cbc06ac03a94/planilha_de_valores_referencia.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f5/d1/f5d1fe09-085a-48f0-9a1c-2802cf4ca1a2/dou_pe_6-2023_adiamento_publicado_em_24022023.pdf</t>
         </is>
       </c>
       <c r="J180" t="n">
@@ -10371,7 +10371,7 @@
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10391,13 +10391,13 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>CR 25/2023 - Reforma e Modernização - Espaço SESI Inovação — Material Técnico Stripscreen</t>
+          <t>PE 06/2023 - Plataforma sistema SESI de educação Adaptativo Digital — Empresas participantes</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Concorrência | Encerrado/Concluído | Abertura: 2023-03-03 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-27 | Participantes</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>manual_tecnico_stripscreen.pdf</t>
+          <t>relatoriomapacomparativoprecos_10.pdf</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/95/04/95042680-31f4-468a-964f-c57c5793c943/manual_tecnico_stripscreen.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/6d/4b/6d4b5851-3720-4564-a446-263854c85282/relatoriomapacomparativoprecos_10.pdf</t>
         </is>
       </c>
       <c r="J181" t="n">
@@ -10426,7 +10426,7 @@
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10446,13 +10446,13 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>CR 25/2023 - Reforma e Modernização - Espaço SESI Inovação — Planilha referencia de orçamento com valores - BDI Diferenciado</t>
+          <t>Edital PE 5/2023 -  Serviço de vigilância — Participantes PE 05/2023</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Concorrência | Encerrado/Concluído | Abertura: 2023-03-03 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-10 | Participantes</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>planilha_referencia_de_orcamento_com_valores_-_bdi_diferenciado.pdf</t>
+          <t>participantes_pe_05-2023.pdf</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/0a/78/0a7888b7-5aff-49d9-95bb-6dbb59923df9/planilha_referencia_de_orcamento_com_valores_-_bdi_diferenciado.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/eb/48/eb48c7d9-594e-4b32-95fc-9beb6b0ed564/participantes_pe_05-2023.pdf</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -10481,7 +10481,7 @@
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10501,13 +10501,13 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PE 06/2023 - Plataforma sistema SESI de educação Adaptativo Digital — Anexo III Contrato - Condições Gerais</t>
+          <t>PE 14/2023 - Locação de equipamento Festival de Robótica — Empresas Participantes</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-27 | Edital/Chamamento</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-08 | Participantes</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>contrato_de_prestacao_de_servicos_-_condicoes_gerais_cnisesisenaiiel.pdf</t>
+          <t>participantes_pe_14-2023.pdf</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/1a/2a/1a2a0f5c-1a77-489f-85d3-befedfd2ed20/contrato_de_prestacao_de_servicos_-_condicoes_gerais_cnisesisenaiiel.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/e9/ca/e9ca4846-56fc-4e45-a582-b315c8400663/participantes_pe_14-2023.pdf</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -10536,7 +10536,7 @@
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10556,13 +10556,13 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>PE 06/2023 - Plataforma sistema SESI de educação Adaptativo Digital — Aviso de Adiamento</t>
+          <t>Edital PE 10/2023 -  Serviços de limpeza — Publicação do certame</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-27 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-07 | Outros Documentos</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>dou_pe_6-2023_adiamento_publicado_em_24022023.pdf</t>
+          <t>dou_pe_10-2023_-_publicado_em_30012023.pdf</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f5/d1/f5d1fe09-085a-48f0-9a1c-2802cf4ca1a2/dou_pe_6-2023_adiamento_publicado_em_24022023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/70/37/70370e80-f7ee-4a94-8e37-a1c013c45769/dou_pe_10-2023_-_publicado_em_30012023.pdf</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -10591,7 +10591,7 @@
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10611,13 +10611,13 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>PE 06/2023 - Plataforma sistema SESI de educação Adaptativo Digital — Empresas participantes</t>
+          <t>Edital PE 10/2023 -  Serviços de limpeza — Empresa e valor</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-27 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-07 | Outros Documentos</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -10627,12 +10627,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>relatoriomapacomparativoprecos_10.pdf</t>
+          <t>relatorio_mapacomparativoprecos.pdf</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/6d/4b/6d4b5851-3720-4564-a446-263854c85282/relatoriomapacomparativoprecos_10.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/fd/fb/fdfba828-4f1b-4e07-9778-17f1e2c5c01f/relatorio_mapacomparativoprecos.pdf</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -10646,7 +10646,7 @@
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10666,13 +10666,13 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Edital PE 5/2023 -  Serviço de vigilância — Participantes PE 05/2023</t>
+          <t>Edital PE 11/2022 -  Serviços de Prevenção e combate a incêndio — Publicação do certame</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-10 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-07 | Outros Documentos</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -10682,12 +10682,12 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>participantes_pe_05-2023.pdf</t>
+          <t>dou_pe_11-2023_-_publicado_em_30012023.pdf</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/eb/48/eb48c7d9-594e-4b32-95fc-9beb6b0ed564/participantes_pe_05-2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/9d/e1/9de17743-0ff9-4550-82d6-aefcc30ea94b/dou_pe_11-2023_-_publicado_em_30012023.pdf</t>
         </is>
       </c>
       <c r="J186" t="n">
@@ -10701,7 +10701,7 @@
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10721,13 +10721,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>PE 14/2023 - Locação de equipamento Festival de Robótica — Empresas Participantes</t>
+          <t>Edital PE 11/2022 -  Serviços de Prevenção e combate a incêndio — Empresa e valor</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-08 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-07 | Outros Documentos</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>participantes_pe_14-2023.pdf</t>
+          <t>relatorio_mapacomparativoprecos.pdf</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/e9/ca/e9ca4846-56fc-4e45-a582-b315c8400663/participantes_pe_14-2023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/5e/64/5e64f3ec-34fb-47f8-b1f4-cc87f97ef708/relatorio_mapacomparativoprecos.pdf</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -10756,7 +10756,7 @@
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10776,13 +10776,13 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Edital PE 10/2023 -  Serviços de limpeza — Publicação do certame</t>
+          <t>PP 67/2022 - Avaliação em Larga Escala — Publicação_DOU</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-07 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-12-12 | Outros Documentos</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>dou_pe_10-2023_-_publicado_em_30012023.pdf</t>
+          <t>dou_pp_67-2022_publi_18112022.pdf</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/70/37/70370e80-f7ee-4a94-8e37-a1c013c45769/dou_pe_10-2023_-_publicado_em_30012023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/d6/4f/d64fd73b-e805-4778-9e41-4ed445ce5193/dou_pp_67-2022_publi_18112022.pdf</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -10811,7 +10811,7 @@
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10831,13 +10831,13 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Edital PE 10/2023 -  Serviços de limpeza — Empresa e valor</t>
+          <t>PP 67/2022 - Avaliação em Larga Escala — Aviso de Suspensão</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-07 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-12-12 | Outros Documentos</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>relatorio_mapacomparativoprecos.pdf</t>
+          <t>dou_pp_67-2022_suspensao_publi_24112022.pdf</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/fd/fb/fdfba828-4f1b-4e07-9778-17f1e2c5c01f/relatorio_mapacomparativoprecos.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/57/16/5716f0b2-bccf-4cc7-b942-54e23eccbe63/dou_pp_67-2022_suspensao_publi_24112022.pdf</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -10866,7 +10866,7 @@
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10886,13 +10886,13 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Edital PE 11/2022 -  Serviços de Prevenção e combate a incêndio — Publicação do certame</t>
+          <t>PP 67/2022 - Avaliação em Larga Escala — Publicação DOU_reagendamento_nova data</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-07 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-12-12 | Outros Documentos</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>dou_pe_11-2023_-_publicado_em_30012023.pdf</t>
+          <t>dou_pp_67-2022_reagendamento_-publ_02122022.pdf</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/9d/e1/9de17743-0ff9-4550-82d6-aefcc30ea94b/dou_pe_11-2023_-_publicado_em_30012023.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/1c/d8/1cd83e2b-976b-4088-a6cd-1601890161d7/dou_pp_67-2022_reagendamento_-publ_02122022.pdf</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -10921,7 +10921,7 @@
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10941,13 +10941,13 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Edital PE 11/2022 -  Serviços de Prevenção e combate a incêndio — Empresa e valor</t>
+          <t>Edital CR 95/2022 - Solução de Gestão de Segurança e Saúde no Trabalh — Publicação_DOU</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2023-02-07 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Concorrência | Encerrado/Concluído | Abertura: 2022-12-05 | Outros Documentos</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>relatorio_mapacomparativoprecos.pdf</t>
+          <t>dou_cr_95-2022_-_publ_16112022.pdf</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/5e/64/5e64f3ec-34fb-47f8-b1f4-cc87f97ef708/relatorio_mapacomparativoprecos.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/b5/a5/b5a52088-da8c-4815-b5fd-97051d69e6fa/dou_cr_95-2022_-_publ_16112022.pdf</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -10976,7 +10976,7 @@
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -10996,13 +10996,13 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>PP 67/2022 - Avaliação em Larga Escala — Publicação_DOU</t>
+          <t>Edital PE 78/2022 - Locação de Notebooks — Julgamento dos Recursos</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-12-12 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-12-01 | Outros Documentos</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>dou_pp_67-2022_publi_18112022.pdf</t>
+          <t>pe_78-2022_-_julgamento_convex__-_simpress.pdf</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/d6/4f/d64fd73b-e805-4778-9e41-4ed445ce5193/dou_pp_67-2022_publi_18112022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/14/74/1474f3a8-08fc-4455-b08a-f5ece10217aa/pe_78-2022_-_julgamento_convex__-_simpress.pdf</t>
         </is>
       </c>
       <c r="J192" t="n">
@@ -11031,7 +11031,7 @@
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11051,13 +11051,13 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>PP 67/2022 - Avaliação em Larga Escala — Aviso de Suspensão</t>
+          <t>Edital PE 78/2022 - Locação de Notebooks — Empresas Participantes e Preços</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-12-12 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-12-01 | Participantes</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11067,12 +11067,12 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>dou_pp_67-2022_suspensao_publi_24112022.pdf</t>
+          <t>empresas_participantes_e_precos.pdf</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/57/16/5716f0b2-bccf-4cc7-b942-54e23eccbe63/dou_pp_67-2022_suspensao_publi_24112022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/fd/b9/fdb98a47-f15f-4392-9c81-c809d5614f9b/empresas_participantes_e_precos.pdf</t>
         </is>
       </c>
       <c r="J193" t="n">
@@ -11086,7 +11086,7 @@
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11106,13 +11106,13 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>PP 67/2022 - Avaliação em Larga Escala — Publicação DOU_reagendamento_nova data</t>
+          <t>PE 96/2022 - Manutenção tecnológica — CANCELAMENTO</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-12-12 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-11-24 | Outros Documentos</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>dou_pp_67-2022_reagendamento_-publ_02122022.pdf</t>
+          <t>dou_pe_96-2022_cancelamento_em_07122022.pdf</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/1c/d8/1cd83e2b-976b-4088-a6cd-1601890161d7/dou_pp_67-2022_reagendamento_-publ_02122022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/46/8a/468a5a1e-5bb6-4268-babc-eaed508cf4e2/dou_pe_96-2022_cancelamento_em_07122022.pdf</t>
         </is>
       </c>
       <c r="J194" t="n">
@@ -11141,7 +11141,7 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11161,13 +11161,13 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Edital CR 95/2022 - Solução de Gestão de Segurança e Saúde no Trabalh — Publicação_DOU</t>
+          <t>PE 71/2022 - Sistema de sinalização interna do SESI Lab. — Participantes PE 71/2022</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Concorrência | Encerrado/Concluído | Abertura: 2022-12-05 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-09-22 | Participantes</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -11177,12 +11177,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>dou_cr_95-2022_-_publ_16112022.pdf</t>
+          <t>participantes_pe-71-2022.pdf</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/b5/a5/b5a52088-da8c-4815-b5fd-97051d69e6fa/dou_cr_95-2022_-_publ_16112022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/c1/04/c1043d6a-eff8-44e5-9dce-5268b3f8c6fd/participantes_pe-71-2022.pdf</t>
         </is>
       </c>
       <c r="J195" t="n">
@@ -11196,7 +11196,7 @@
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11216,13 +11216,13 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Edital PE 78/2022 - Locação de Notebooks — Julgamento dos Recursos</t>
+          <t>PE 45/2022-Contratação de empresa especializada para oferta de curso — Participantes PE 45/2022</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-12-01 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-09-20 | Participantes</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>pe_78-2022_-_julgamento_convex__-_simpress.pdf</t>
+          <t>participantes_pe_45-2022.pdf</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/14/74/1474f3a8-08fc-4455-b08a-f5ece10217aa/pe_78-2022_-_julgamento_convex__-_simpress.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/23/64/23648554-02c8-48b5-b68f-5e7b2bf90436/participantes_pe_45-2022.pdf</t>
         </is>
       </c>
       <c r="J196" t="n">
@@ -11251,7 +11251,7 @@
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11271,13 +11271,13 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Edital PE 78/2022 - Locação de Notebooks — Empresas Participantes e Preços</t>
+          <t>Edital PE 74/2022 - Bilheteria Digital — Participantes PE-74/2022</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-12-01 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-09-05 | Participantes</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>empresas_participantes_e_precos.pdf</t>
+          <t>participantes_pe_74-2022.pdf</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/fd/b9/fdb98a47-f15f-4392-9c81-c809d5614f9b/empresas_participantes_e_precos.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/10/06/1006730c-74e1-43d1-af8d-fe0a044edfc6/participantes_pe_74-2022.pdf</t>
         </is>
       </c>
       <c r="J197" t="n">
@@ -11306,7 +11306,7 @@
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11326,13 +11326,13 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>PE 96/2022 - Manutenção tecnológica — CANCELAMENTO</t>
+          <t>PP 63/2022 - PONTOS DE ACESSO PARA REDE WI-FI (ACCESS POINT) — AVISO DE CANCELAMENTO.</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-11-24 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-08-10 | Outros Documentos</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>dou_pe_96-2022_cancelamento_em_07122022.pdf</t>
+          <t>dou_-_pp_63-2022_-_cancelamento_-_publicado_em_18082022.pdf</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/46/8a/468a5a1e-5bb6-4268-babc-eaed508cf4e2/dou_pe_96-2022_cancelamento_em_07122022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/07/fb/07fbaf3d-384b-4821-93f6-dec87e39e019/dou_-_pp_63-2022_-_cancelamento_-_publicado_em_18082022.pdf</t>
         </is>
       </c>
       <c r="J198" t="n">
@@ -11361,7 +11361,7 @@
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11381,13 +11381,13 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>PE 71/2022 - Sistema de sinalização interna do SESI Lab. — Participantes PE 71/2022</t>
+          <t>Edital PE 49/2022 - Aquisição de Catracas — Empresas Participantes</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-09-22 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-08-03 | Participantes</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>participantes_pe-71-2022.pdf</t>
+          <t>participantes_pe_49-2022.pdf</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/c1/04/c1043d6a-eff8-44e5-9dce-5268b3f8c6fd/participantes_pe-71-2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/a1/62/a162274f-d11c-4516-9569-3fcbad762e17/participantes_pe_49-2022.pdf</t>
         </is>
       </c>
       <c r="J199" t="n">
@@ -11416,7 +11416,7 @@
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11436,13 +11436,13 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>PE 45/2022-Contratação de empresa especializada para oferta de curso — Participantes PE 45/2022</t>
+          <t>PP 26/2022 SOLUÇÃO EDUCACIONAL DIGITAL — AVISO DE ADIAMENTO</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-09-20 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-07-29 | Outros Documentos</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -11452,12 +11452,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>participantes_pe_45-2022.pdf</t>
+          <t>pp_26-2022_adiamento_publicado_em_25072022.pdf</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/23/64/23648554-02c8-48b5-b68f-5e7b2bf90436/participantes_pe_45-2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/29/00/2900131e-c9df-4a03-9fee-3dfb952582bc/pp_26-2022_adiamento_publicado_em_25072022.pdf</t>
         </is>
       </c>
       <c r="J200" t="n">
@@ -11471,7 +11471,7 @@
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11491,13 +11491,13 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Edital PE 74/2022 - Bilheteria Digital — Participantes PE-74/2022</t>
+          <t>PE 47/2022 - Contratação Kit Robótica - First LEGO League Challenge — AVISO DE ADIAMENTO</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-09-05 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-07-27 | Outros Documentos</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>participantes_pe_74-2022.pdf</t>
+          <t>dou_pe_47-2022_-_adiamento_-publicado_em_22072022.pdf</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/10/06/1006730c-74e1-43d1-af8d-fe0a044edfc6/participantes_pe_74-2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/77/4a/774af463-ea35-4b3d-bcc7-a09adeeff458/dou_pe_47-2022_-_adiamento_-publicado_em_22072022.pdf</t>
         </is>
       </c>
       <c r="J201" t="n">
@@ -11526,7 +11526,7 @@
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11546,13 +11546,13 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>PP 63/2022 - PONTOS DE ACESSO PARA REDE WI-FI (ACCESS POINT) — AVISO DE CANCELAMENTO.</t>
+          <t>PE 47/2022 - Contratação Kit Robótica - First LEGO League Challenge — Participantes PE 47/2021</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-08-10 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-07-27 | Participantes</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>dou_-_pp_63-2022_-_cancelamento_-_publicado_em_18082022.pdf</t>
+          <t>participantes_pe-47-2022.pdf</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/07/fb/07fbaf3d-384b-4821-93f6-dec87e39e019/dou_-_pp_63-2022_-_cancelamento_-_publicado_em_18082022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/50/ca/50ca25ad-b195-4261-8699-3ba21452f62f/participantes_pe-47-2022.pdf</t>
         </is>
       </c>
       <c r="J202" t="n">
@@ -11581,7 +11581,7 @@
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11601,13 +11601,13 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Edital PE 49/2022 - Aquisição de Catracas — Empresas Participantes</t>
+          <t>PE 57/2022 - SERVIÇO DE LOCAÇÃO DE EQUIPAMENTO ÁUDIO VIDEO — Participantes PE 57/2022</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-08-03 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-07-19 | Participantes</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -11617,12 +11617,12 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>participantes_pe_49-2022.pdf</t>
+          <t>participantes_pe_57-2022.pdf</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/a1/62/a162274f-d11c-4516-9569-3fcbad762e17/participantes_pe_49-2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/91/65/91656fb9-f491-4f60-b5ae-030017481096/participantes_pe_57-2022.pdf</t>
         </is>
       </c>
       <c r="J203" t="n">
@@ -11636,7 +11636,7 @@
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11656,13 +11656,13 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>PP 26/2022 SOLUÇÃO EDUCACIONAL DIGITAL — AVISO DE ADIAMENTO</t>
+          <t>PP 40/2022 - PONTOS DE ACESSO PARA REDE WI-FI (ACCESS POINT) — AVISO DE CANCELAMENTO</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-07-29 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-07-17 | Outros Documentos</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>pp_26-2022_adiamento_publicado_em_25072022.pdf</t>
+          <t>aviso_de_cancelamento_-_dou_28072022.pdf</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/29/00/2900131e-c9df-4a03-9fee-3dfb952582bc/pp_26-2022_adiamento_publicado_em_25072022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/af/e8/afe8e8a0-17bd-4ef2-a2d6-93f6ceae3663/aviso_de_cancelamento_-_dou_28072022.pdf</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -11691,7 +11691,7 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11711,13 +11711,13 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>PE 47/2022 - Contratação Kit Robótica - First LEGO League Challenge — AVISO DE ADIAMENTO</t>
+          <t>PP 55/2022 - Mobiliário Escolar — Ata_Republicação</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-07-27 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-07-11 | Outros Documentos</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>dou_pe_47-2022_-_adiamento_-publicado_em_22072022.pdf</t>
+          <t>ata_-_pp_n55_-2022-_republicacao.pdf</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/77/4a/774af463-ea35-4b3d-bcc7-a09adeeff458/dou_pe_47-2022_-_adiamento_-publicado_em_22072022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/94/fb/94fb35f7-2d50-4d6c-93d4-2576e2f6d3a1/ata_-_pp_n55_-2022-_republicacao.pdf</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -11746,7 +11746,7 @@
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11766,13 +11766,13 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>PE 47/2022 - Contratação Kit Robótica - First LEGO League Challenge — Participantes PE 47/2021</t>
+          <t>PP 55/2022 - Mobiliário Escolar — Publicação_nova data: 11/07/2022</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-07-27 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-07-11 | Outros Documentos</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>participantes_pe-47-2022.pdf</t>
+          <t>dou_pp-552022_-republicacao_-publicado_em_01072022.pdf</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/50/ca/50ca25ad-b195-4261-8699-3ba21452f62f/participantes_pe-47-2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/1b/98/1b981575-4941-4bbc-9621-084b7b66a584/dou_pp-552022_-republicacao_-publicado_em_01072022.pdf</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -11801,7 +11801,7 @@
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11821,13 +11821,13 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>PE 57/2022 - SERVIÇO DE LOCAÇÃO DE EQUIPAMENTO ÁUDIO VIDEO — Participantes PE 57/2022</t>
+          <t>PE 37/2022 - LICENÇA DE SOFTWARE — AVISO_ERRATA_DOU</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-07-19 | Participantes</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-06-20 | Outros Documentos</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -11837,12 +11837,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>participantes_pe_57-2022.pdf</t>
+          <t>pe_37-2022_-_errata_publicado_em_08062022.pdf</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/91/65/91656fb9-f491-4f60-b5ae-030017481096/participantes_pe_57-2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/55/55/5555a888-eb9b-43af-abd5-f03dbe7ac46e/pe_37-2022_-_errata_publicado_em_08062022.pdf</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -11856,7 +11856,7 @@
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11876,13 +11876,13 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>PP 40/2022 - PONTOS DE ACESSO PARA REDE WI-FI (ACCESS POINT) — AVISO DE CANCELAMENTO</t>
+          <t>PE 37/2022 - LICENÇA DE SOFTWARE — Participantes PE 37/2022</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-07-17 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-06-20 | Participantes</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -11892,12 +11892,12 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>aviso_de_cancelamento_-_dou_28072022.pdf</t>
+          <t>participantes_pe-37-2022.pdf</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/af/e8/afe8e8a0-17bd-4ef2-a2d6-93f6ceae3663/aviso_de_cancelamento_-_dou_28072022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/1a/05/1a05fafd-e0b1-463f-9924-8412e53002bd/participantes_pe-37-2022.pdf</t>
         </is>
       </c>
       <c r="J208" t="n">
@@ -11911,7 +11911,7 @@
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11931,13 +11931,13 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>PP 55/2022 - Mobiliário Escolar — Ata_Republicação</t>
+          <t>PE 46/2022 - AQUISIÇÃO DE NOTEBOOK — Participantes PE 46/2022</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-07-11 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-05-23 | Participantes</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>ata_-_pp_n55_-2022-_republicacao.pdf</t>
+          <t>participantes_pe_46-2022.pdf</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/94/fb/94fb35f7-2d50-4d6c-93d4-2576e2f6d3a1/ata_-_pp_n55_-2022-_republicacao.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/01/a2/01a2d102-d617-447f-a432-ed04e43c59b7/participantes_pe_46-2022.pdf</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -11966,7 +11966,7 @@
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -11986,13 +11986,13 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>PP 55/2022 - Mobiliário Escolar — Publicação_nova data: 11/07/2022</t>
+          <t>PE 17/2022 - SERVIÇO DE CENOGRAFIA — Participantes PE 17/2022</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Presencial | Encerrado/Concluído | Abertura: 2022-07-11 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-04-18 | Participantes</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>dou_pp-552022_-republicacao_-publicado_em_01072022.pdf</t>
+          <t>participantes_pe-17-2022.pdf</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/1b/98/1b981575-4941-4bbc-9621-084b7b66a584/dou_pp-552022_-republicacao_-publicado_em_01072022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/f9/a9/f9a9d98a-ac41-44e8-af09-1a2b31038aee/participantes_pe-17-2022.pdf</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -12021,7 +12021,7 @@
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -12041,13 +12041,13 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>PE 37/2022 - LICENÇA DE SOFTWARE — AVISO_ERRATA_DOU</t>
+          <t>PE 26/2021 - Gestão e governança corporativa em tecnologia. — Participantes PE 26/2021</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-06-20 | Outros Documentos</t>
+          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2021-09-30 | Participantes</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>pe_37-2022_-_errata_publicado_em_08062022.pdf</t>
+          <t>participantes_pe_26-2021.pdf</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/55/55/5555a888-eb9b-43af-abd5-f03dbe7ac46e/pe_37-2022_-_errata_publicado_em_08062022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/90/d4/90d4f069-0607-4e43-af9b-261b8effa910/participantes_pe_26-2021.pdf</t>
         </is>
       </c>
       <c r="J211" t="n">
@@ -12076,7 +12076,7 @@
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -12091,18 +12091,18 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Processos de contratação</t>
+          <t>Informações de Empregados e Dirigentes</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>PE 37/2022 - LICENÇA DE SOFTWARE — Participantes PE 37/2022</t>
+          <t>Relação de dirigentes 2024 - PDF 53 Kb</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-06-20 | Participantes</t>
+          <t>Informações de Empregados e Dirigentes</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>participantes_pe-37-2022.pdf</t>
+          <t>sesi_rel_dirig_2024.pdf</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/1a/05/1a05fafd-e0b1-463f-9924-8412e53002bd/participantes_pe-37-2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/9c/3f/9c3f163f-40d9-44f4-9ba5-ae9beb6dbb42/sesi_rel_dirig_2024.pdf</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -12131,7 +12131,7 @@
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -12146,18 +12146,18 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Processos de contratação</t>
+          <t>Informações de Empregados e Dirigentes</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>PE 46/2022 - AQUISIÇÃO DE NOTEBOOK — Participantes PE 46/2022</t>
+          <t>Relação de dirigentes 2023 - PDF 54 Kb</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-05-23 | Participantes</t>
+          <t>Informações de Empregados e Dirigentes</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>participantes_pe_46-2022.pdf</t>
+          <t>sesi_rel_dirig_2023.pdf</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/01/a2/01a2d102-d617-447f-a432-ed04e43c59b7/participantes_pe_46-2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/a9/1f/a91f834d-1d8a-43aa-a020-26f6c248ccbf/sesi_rel_dirig_2023.pdf</t>
         </is>
       </c>
       <c r="J213" t="n">
@@ -12186,7 +12186,7 @@
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -12201,18 +12201,18 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Processos de contratação</t>
+          <t>Informações de Empregados e Dirigentes</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>PE 17/2022 - SERVIÇO DE CENOGRAFIA — Participantes PE 17/2022</t>
+          <t>Relação de dirigentes 2022 - PDF 53 Kb</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2022-04-18 | Participantes</t>
+          <t>Informações de Empregados e Dirigentes</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>participantes_pe-17-2022.pdf</t>
+          <t>sesi_rel_dirig_2022.pdf</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/f9/a9/f9a9d98a-ac41-44e8-af09-1a2b31038aee/participantes_pe-17-2022.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/73/ab/73ab5545-2096-4023-8808-925a5af7587b/sesi_rel_dirig_2022.pdf</t>
         </is>
       </c>
       <c r="J214" t="n">
@@ -12241,7 +12241,7 @@
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
@@ -12256,18 +12256,18 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Processos de contratação</t>
+          <t>Informações de Empregados e Dirigentes</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>PE 26/2021 - Gestão e governança corporativa em tecnologia. — Participantes PE 26/2021</t>
+          <t>Plano de Cargos e Salários 183 Kb</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Processos de contratação | SESI | RLC Pregão Eletrônico | Encerrado/Concluído | Abertura: 2021-09-30 | Participantes</t>
+          <t>Informações de Empregados e Dirigentes</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>participantes_pe_26-2021.pdf</t>
+          <t>resumo_pccr_para_transparencia_lai_sesi.pdf</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/90/d4/90d4f069-0607-4e43-af9b-261b8effa910/participantes_pe_26-2021.pdf</t>
+          <t>https://static.portaldaindustria.com.br/media/filer_public/23/02/230271b7-8118-4352-8acf-5e4a7fcced96/resumo_pccr_para_transparencia_lai_sesi.pdf</t>
         </is>
       </c>
       <c r="J215" t="n">
@@ -12296,227 +12296,7 @@
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2026-09-15 17:03:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>215</v>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>SESI_PDF</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Informações de Empregados e Dirigentes</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Relação de dirigentes 2024 - PDF 53 Kb</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Informações de Empregados e Dirigentes</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>sesi_rel_dirig_2024.pdf</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/9c/3f/9c3f163f-40d9-44f4-9ba5-ae9beb6dbb42/sesi_rel_dirig_2024.pdf</t>
-        </is>
-      </c>
-      <c r="J216" t="n">
-        <v>200</v>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>2026-09-15 17:03:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>216</v>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>SESI_PDF</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Informações de Empregados e Dirigentes</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Relação de dirigentes 2023 - PDF 54 Kb</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Informações de Empregados e Dirigentes</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>sesi_rel_dirig_2023.pdf</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/a9/1f/a91f834d-1d8a-43aa-a020-26f6c248ccbf/sesi_rel_dirig_2023.pdf</t>
-        </is>
-      </c>
-      <c r="J217" t="n">
-        <v>200</v>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>2026-09-15 17:03:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
-        <v>217</v>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>SESI_PDF</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Informações de Empregados e Dirigentes</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>Relação de dirigentes 2022 - PDF 53 Kb</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>Informações de Empregados e Dirigentes</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>sesi_rel_dirig_2022.pdf</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/73/ab/73ab5545-2096-4023-8808-925a5af7587b/sesi_rel_dirig_2022.pdf</t>
-        </is>
-      </c>
-      <c r="J218" t="n">
-        <v>200</v>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>2026-09-15 17:03:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>218</v>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>SESI_PDF</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Informações de Empregados e Dirigentes</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Plano de Cargos e Salários 183 Kb</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>Informações de Empregados e Dirigentes</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>resumo_pccr_para_transparencia_lai_sesi.pdf</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>https://static.portaldaindustria.com.br/media/filer_public/23/02/230271b7-8118-4352-8acf-5e4a7fcced96/resumo_pccr_para_transparencia_lai_sesi.pdf</t>
-        </is>
-      </c>
-      <c r="J219" t="n">
-        <v>200</v>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>2026-09-15 17:03:36</t>
+          <t>2026-09-29 16:19:10</t>
         </is>
       </c>
     </row>
